--- a/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0074.xlsx
+++ b/mistral_translate_work/split_by_prompt/excel/name_title/lang_multi_text/lang_multi_text__name_title__part_0074.xlsx
@@ -644,7 +644,7 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>Đường Đua Vô Tận Dải Ngân Hà</t>
+          <t>Đường Đua Dải Ngân Hà Vô Tận</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
@@ -714,7 +714,7 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>Chuyến Tham quan Tìm Kiếm Dải Ngân Hà</t>
+          <t>Chuyến Du Ngoạn Kiếm Thức Thiên Hà</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>Nảy Bóng Sao</t>
+          <t>Vụ nổ sao</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -854,7 +854,7 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>Hoàn thành giai đoạn yêu cầu để mở khóa</t>
+          <t>Hoàn thành giai đoạn yêu cầu để mở khóa.</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
@@ -924,7 +924,7 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>Taoyuan Vale 1</t>
+          <t>Thung Lũng Đào Nguyên 1</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
@@ -994,7 +994,7 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>Taoyuan Vale 2</t>
+          <t>Thung Lũng Đào Nguyên 2</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
@@ -1064,7 +1064,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>Taoyuan Vale 3</t>
+          <t>Thung Lũng Đào Nguyên 3</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1134,7 +1134,7 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>Taoyuan Vale 4</t>
+          <t>Thung Lũng Taoyuan 4</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
@@ -1204,7 +1204,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>Norfall Barrens 1</t>
+          <t>Bãi Hoang Norfall 1</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1274,7 +1274,7 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
-          <t>Norfall Barrens 2</t>
+          <t>Bãi Hoang Norfall 2</t>
         </is>
       </c>
       <c r="N12" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>Norfall Barrens 3</t>
+          <t>Bãi Hoang Norfall 3</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1414,7 +1414,7 @@
       </c>
       <c r="M14" t="inlineStr">
         <is>
-          <t>Norfall Barrens 4</t>
+          <t>Bãi Hoang Norfall 4</t>
         </is>
       </c>
       <c r="N14" t="inlineStr">
@@ -2114,7 +2114,7 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>Honami City 2</t>
+          <t>Thành phố Honami 2</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
@@ -2184,7 +2184,7 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>Honami City 3</t>
+          <t>Thành phố Honami 3</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
@@ -2254,7 +2254,7 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>Honami City 4</t>
+          <t>Thành phố Honami 4</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>Startorch Academy 1</t>
+          <t>Học viện Startorch 1</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2394,7 +2394,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>Startorch Academy 2</t>
+          <t>Học viện Startorch 2</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2464,7 +2464,7 @@
       </c>
       <c r="M29" t="inlineStr">
         <is>
-          <t>Startorch Academy 3</t>
+          <t>Học viện Startorch 3</t>
         </is>
       </c>
       <c r="N29" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>Startorch Academy 4</t>
+          <t>Học viện Startorch 4</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
@@ -2604,7 +2604,7 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>Roya Frostlands 1</t>
+          <t>Lãnh Nguyên Roya 1</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
@@ -2674,7 +2674,7 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>Roya Frostlands 2</t>
+          <t>Lãnh Nguyên Roya 2</t>
         </is>
       </c>
       <c r="N32" t="inlineStr">
@@ -2744,7 +2744,7 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>Roya Frostlands 3</t>
+          <t>Vùng Đất Băng Giá Roya 3</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
@@ -2814,7 +2814,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>Roya Frostlands 4</t>
+          <t>Vùng Đất Băng Giá Roya 4</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3164,7 +3164,7 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>Chuyến Tham quan Tìm Kiếm Dải Ngân Hà</t>
+          <t>Chuyến Du Ngoạn Kiếm Thức Thiên Hà</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
@@ -3234,7 +3234,7 @@
       </c>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 1</t>
+          <t>Đường Đua Dải Ngân Hà Vô Tận 1</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -3304,7 +3304,7 @@
       </c>
       <c r="M41" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 2</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 2</t>
         </is>
       </c>
       <c r="N41" t="inlineStr">
@@ -3374,7 +3374,7 @@
       </c>
       <c r="M42" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 3</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 3</t>
         </is>
       </c>
       <c r="N42" t="inlineStr">
@@ -3444,7 +3444,7 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 4</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 4</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 5</t>
+          <t>Bản nhạc Ngân Hà Bất Tận 5</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
@@ -3584,7 +3584,7 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 6</t>
+          <t>Bản nhạc Ngân Hà Bất Tận 6</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
@@ -3654,7 +3654,7 @@
       </c>
       <c r="M46" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 7</t>
+          <t>Bản nhạc Ngân Hà Bất Tận 7</t>
         </is>
       </c>
       <c r="N46" t="inlineStr">
@@ -3724,7 +3724,7 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 8</t>
+          <t>Bản nhạc Ngân Hà Bất Tận 8</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
@@ -3794,7 +3794,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 9</t>
+          <t>Bản nhạc Ngân Hà Bất Tận 9</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -3864,7 +3864,7 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 10</t>
+          <t>Đường Đua Dải Ngân Hà Vô Tận 10</t>
         </is>
       </c>
       <c r="N49" t="inlineStr">
@@ -3934,7 +3934,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 11</t>
+          <t>Đường Đua Dải Ngân Hà Vô Tận 11</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4004,7 +4004,7 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 12</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 12</t>
         </is>
       </c>
       <c r="N51" t="inlineStr">
@@ -4074,7 +4074,7 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 13</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 13</t>
         </is>
       </c>
       <c r="N52" t="inlineStr">
@@ -4144,7 +4144,7 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 14</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 14</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 15</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 15</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="M55" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 16</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 16</t>
         </is>
       </c>
       <c r="N55" t="inlineStr">
@@ -4354,7 +4354,7 @@
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 17</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 17</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
@@ -4424,7 +4424,7 @@
       </c>
       <c r="M57" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 18</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 18</t>
         </is>
       </c>
       <c r="N57" t="inlineStr">
@@ -4494,7 +4494,7 @@
       </c>
       <c r="M58" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 19</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 19</t>
         </is>
       </c>
       <c r="N58" t="inlineStr">
@@ -4564,7 +4564,7 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>Endless Galaxy Track 20</t>
+          <t>Bản nhạc Dải Ngân Hà Bất Tận 20</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
@@ -4634,7 +4634,7 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>Dọn sạch sân khấu</t>
+          <t>Hoàn thành màn chơi</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
@@ -4704,7 +4704,7 @@
       </c>
       <c r="M61" t="inlineStr">
         <is>
-          <t>Pinball Master</t>
+          <t>Bậc Thầy Pinball</t>
         </is>
       </c>
       <c r="N61" t="inlineStr">
@@ -4774,7 +4774,7 @@
       </c>
       <c r="M62" t="inlineStr">
         <is>
-          <t>Physics Engine Wiz</t>
+          <t>Chuyên Gia Vật Lý Động Học</t>
         </is>
       </c>
       <c r="N62" t="inlineStr">
@@ -4984,7 +4984,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>Elite</t>
+          <t>Tinh Anh</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5054,7 +5054,7 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>Boss</t>
+          <t>Trùm</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
@@ -5124,7 +5124,7 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>Prism Formation</t>
+          <t>Hình Thành Lăng Kính</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
@@ -5194,7 +5194,7 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>Kỹ năng 1</t>
+          <t>Skill 1</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
@@ -5264,7 +5264,7 @@
       </c>
       <c r="M69" t="inlineStr">
         <is>
-          <t>Kỹ năng 2</t>
+          <t>Skill 2</t>
         </is>
       </c>
       <c r="N69" t="inlineStr">
@@ -5334,7 +5334,7 @@
       </c>
       <c r="M70" t="inlineStr">
         <is>
-          <t>Kỹ năng 3</t>
+          <t>Skill 3</t>
         </is>
       </c>
       <c r="N70" t="inlineStr">
@@ -5404,7 +5404,7 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>Bounce</t>
+          <t>Nảy</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
@@ -5474,7 +5474,7 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>Rush</t>
+          <t>Xông Pha</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
@@ -5544,7 +5544,7 @@
       </c>
       <c r="M73" t="inlineStr">
         <is>
-          <t>Power Strike</t>
+          <t>Đòn Tấn Công Mạnh</t>
         </is>
       </c>
       <c r="N73" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="M74" t="inlineStr">
         <is>
-          <t>Burst</t>
+          <t>Kích Hoạt</t>
         </is>
       </c>
       <c r="N74" t="inlineStr">
@@ -5684,7 +5684,7 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>Vanguard</t>
+          <t>Tiền Phong</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>Healer</t>
+          <t>Hồi Phục</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
@@ -5894,7 +5894,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>Heal Efficiency</t>
+          <t>Hiệu Suất Hồi Phục</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -5964,7 +5964,7 @@
       </c>
       <c r="M79" t="inlineStr">
         <is>
-          <t>Shield Regen</t>
+          <t>Khiên Tái Tạo</t>
         </is>
       </c>
       <c r="N79" t="inlineStr">
@@ -6034,7 +6034,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>Lên cấp tối đa</t>
+          <t>Tới Cấp Độ Tối Đa</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6174,7 +6174,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>Deduction</t>
+          <t>Suy Luận</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6244,7 +6244,7 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>Passive - Cogitation Model</t>
+          <t>Thụ Động - Mô Hình Suy Tư</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
@@ -6314,7 +6314,7 @@
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>Living Canvas</t>
+          <t>Bức Tranh Sống Động</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
@@ -6384,7 +6384,7 @@
       </c>
       <c r="M85" t="inlineStr">
         <is>
-          <t>Thụ động - Mực Tàu</t>
+          <t>Thụ Động - Mực Tàu Nước Lãng</t>
         </is>
       </c>
       <c r="N85" t="inlineStr">
@@ -6454,7 +6454,7 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>Blade Within Bamboo</t>
+          <t>Kiếm Ẩn Trong Tre</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
@@ -6524,7 +6524,7 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>Passive - Quietude Within</t>
+          <t>Thụ Động - Tĩnh Lặng Nội Tâm</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
@@ -6594,7 +6594,7 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>Emerald Storm</t>
+          <t>Bão Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
@@ -6664,7 +6664,7 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>Thụ động - Cưỡi Gió Cao</t>
+          <t>Thụ Động - Cưỡi Gió Bay Cao</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="M90" t="inlineStr">
         <is>
-          <t>Flaming Sacrifice</t>
+          <t>Hy Sinh Lửa Cháy</t>
         </is>
       </c>
       <c r="N90" t="inlineStr">
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M91" t="inlineStr">
         <is>
-          <t>Passive - Secret Strategist</t>
+          <t>Thụ Động - Chiến Thuật Bí Ẩn</t>
         </is>
       </c>
       <c r="N91" t="inlineStr">
@@ -6874,7 +6874,7 @@
       </c>
       <c r="M92" t="inlineStr">
         <is>
-          <t>Converged Radiance</t>
+          <t>Hào quang hội tụ</t>
         </is>
       </c>
       <c r="N92" t="inlineStr">
@@ -6944,7 +6944,7 @@
       </c>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Passive - Luminal Synthesis</t>
+          <t>Thụ Động - Tổng Hợp Ánh Sáng</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -7014,7 +7014,7 @@
       </c>
       <c r="M94" t="inlineStr">
         <is>
-          <t>Oathbound Hunt</t>
+          <t>Cuộc Săn Đầy Lời Thề</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -7084,7 +7084,7 @@
       </c>
       <c r="M95" t="inlineStr">
         <is>
-          <t>Passive - Flamewing Verdict</t>
+          <t>Thụ Động - Phán Quyết Cánh Lửa</t>
         </is>
       </c>
       <c r="N95" t="inlineStr">
@@ -7154,7 +7154,7 @@
       </c>
       <c r="M96" t="inlineStr">
         <is>
-          <t>Shewolf's Hunt</t>
+          <t>Cuộc Săn Của Sói Cái</t>
         </is>
       </c>
       <c r="N96" t="inlineStr">
@@ -7224,7 +7224,7 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>Passive - Fire-Kissed Glory</t>
+          <t>Thụ Động - Vinh Quang Chạm Lửa</t>
         </is>
       </c>
       <c r="N97" t="inlineStr">
@@ -7294,7 +7294,7 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>Moon Steps</t>
+          <t>Bước Trăng</t>
         </is>
       </c>
       <c r="N98" t="inlineStr">
@@ -7364,7 +7364,7 @@
       </c>
       <c r="M99" t="inlineStr">
         <is>
-          <t>Passive - Derivation</t>
+          <t>Thụ Động - Suy Diễn</t>
         </is>
       </c>
       <c r="N99" t="inlineStr">
@@ -7434,7 +7434,7 @@
       </c>
       <c r="M100" t="inlineStr">
         <is>
-          <t>Harmonic Allegro</t>
+          <t>Hòa Tấu Nhanh</t>
         </is>
       </c>
       <c r="N100" t="inlineStr">
@@ -7504,7 +7504,7 @@
       </c>
       <c r="M101" t="inlineStr">
         <is>
-          <t>Thụ động - Lang Thang Cùng Gió</t>
+          <t>Thụ Động - Lang Thang Cùng Gió</t>
         </is>
       </c>
       <c r="N101" t="inlineStr">
@@ -7574,7 +7574,7 @@
       </c>
       <c r="M102" t="inlineStr">
         <is>
-          <t>Blazing Valor</t>
+          <t>Dũng Khí Bừng Sáng</t>
         </is>
       </c>
       <c r="N102" t="inlineStr">
@@ -7644,7 +7644,7 @@
       </c>
       <c r="M103" t="inlineStr">
         <is>
-          <t>Thụ động - Gọi Ta Bằng Ánh Dương</t>
+          <t>Thụ Động - Gọi Ta Bằng Ánh Mặt Trời</t>
         </is>
       </c>
       <c r="N103" t="inlineStr">
@@ -7714,7 +7714,7 @@
       </c>
       <c r="M104" t="inlineStr">
         <is>
-          <t>Death Snip</t>
+          <t>Cú Chém Tử Thần</t>
         </is>
       </c>
       <c r="N104" t="inlineStr">
@@ -7784,7 +7784,7 @@
       </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>Passive - Inescapable Fate</t>
+          <t>Thụ Động - Định Mệnh Bất Diệt</t>
         </is>
       </c>
       <c r="N105" t="inlineStr">
@@ -7854,7 +7854,7 @@
       </c>
       <c r="M106" t="inlineStr">
         <is>
-          <t>Resolution</t>
+          <t>Quyết Tâm</t>
         </is>
       </c>
       <c r="N106" t="inlineStr">
@@ -7924,7 +7924,7 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>Passive - Blueprint</t>
+          <t>Thụ Động - Bản Thiết Kế</t>
         </is>
       </c>
       <c r="N107" t="inlineStr">
@@ -7994,7 +7994,7 @@
       </c>
       <c r="M108" t="inlineStr">
         <is>
-          <t>Prismatic Overblast</t>
+          <t>Vụ Nổ Sắc Cầu</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -8064,7 +8064,7 @@
       </c>
       <c r="M109" t="inlineStr">
         <is>
-          <t>Passive - Chroma Drift</t>
+          <t>Thụ Động - Trôi Dạt Sắc Màu</t>
         </is>
       </c>
       <c r="N109" t="inlineStr">
@@ -8134,7 +8134,7 @@
       </c>
       <c r="M110" t="inlineStr">
         <is>
-          <t>Dummy Honey</t>
+          <t>Dumdum Yêu Dấu</t>
         </is>
       </c>
       <c r="N110" t="inlineStr">
@@ -8204,7 +8204,7 @@
       </c>
       <c r="M111" t="inlineStr">
         <is>
-          <t>Thụ động - Dấu Vết Của Giả Dối</t>
+          <t>Thụ Động - Dấu Vết Giả Dối</t>
         </is>
       </c>
       <c r="N111" t="inlineStr">
@@ -8274,7 +8274,7 @@
       </c>
       <c r="M112" t="inlineStr">
         <is>
-          <t>Viết Lại Trong Lề Mùa Đông</t>
+          <t>Viết lại trên Lề Mùa Đông</t>
         </is>
       </c>
       <c r="N112" t="inlineStr">
@@ -8344,7 +8344,7 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>Thụ động - Nhịp Đập Dưới Tuyết</t>
+          <t>Thụ Động - Nhịp Đập Dưới Tuyết</t>
         </is>
       </c>
       <c r="N113" t="inlineStr">
@@ -8414,7 +8414,7 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>Infinity Calibration</t>
+          <t>Hiệu Chuẩn Vô Tận</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -8484,7 +8484,7 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>Thụ động - Điêu Khắc Sự Tĩnh Lặng</t>
+          <t>Thụ Động - Dệt Nên Tĩnh Lặng</t>
         </is>
       </c>
       <c r="N115" t="inlineStr">
@@ -8554,7 +8554,7 @@
       </c>
       <c r="M116" t="inlineStr">
         <is>
-          <t>True Names Aligned</t>
+          <t>Chân Danh Đồng Nhất</t>
         </is>
       </c>
       <c r="N116" t="inlineStr">
@@ -8624,7 +8624,7 @@
       </c>
       <c r="M117" t="inlineStr">
         <is>
-          <t>Thụ động - Khoảnh Khắc Rực Rỡ</t>
+          <t>Thụ Động - Khoảnh Khắc Huy Hoàng</t>
         </is>
       </c>
       <c r="N117" t="inlineStr">
@@ -8694,7 +8694,7 @@
       </c>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Frostblight</t>
+          <t>Sương Độc</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -8764,7 +8764,7 @@
       </c>
       <c r="M119" t="inlineStr">
         <is>
-          <t>Passive - Fudoshin</t>
+          <t>Thụ Động - Tâm Bất Động</t>
         </is>
       </c>
       <c r="N119" t="inlineStr">
@@ -8834,7 +8834,7 @@
       </c>
       <c r="M120" t="inlineStr">
         <is>
-          <t>Cấp độ đội quá thấp</t>
+          <t>Cấp đội quá thấp</t>
         </is>
       </c>
       <c r="N120" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="M121" t="inlineStr">
         <is>
-          <t>Cấp Leader Pinball quá thấp</t>
+          <t>Mức Leader Pinball của cậu thấp quá</t>
         </is>
       </c>
       <c r="N121" t="inlineStr">
@@ -8974,7 +8974,7 @@
       </c>
       <c r="M122" t="inlineStr">
         <is>
-          <t>Clear Taoyuan Vale</t>
+          <t>Dọn sạch Thung Lũng Taoyuan</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -9044,7 +9044,7 @@
       </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>Clear Norfall Barrens</t>
+          <t>Hoàn thành Norfall Barrens</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -9114,7 +9114,7 @@
       </c>
       <c r="M124" t="inlineStr">
         <is>
-          <t>Clear Ragunna</t>
+          <t>Đánh bại Ragunna</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Clear Septimont</t>
+          <t>Hoàn thành Septimont</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -9254,7 +9254,7 @@
       </c>
       <c r="M126" t="inlineStr">
         <is>
-          <t>Clear Honami City</t>
+          <t>Dọn sạch Thành Phố Honami</t>
         </is>
       </c>
       <c r="N126" t="inlineStr">
@@ -9324,7 +9324,7 @@
       </c>
       <c r="M127" t="inlineStr">
         <is>
-          <t>Clear Startorch Academy</t>
+          <t>Hoàn thành Startorch Academy</t>
         </is>
       </c>
       <c r="N127" t="inlineStr">
@@ -9394,7 +9394,7 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>Clear Roya Frostlands</t>
+          <t>Hoàn thành Khu Vực Roya Frostlands</t>
         </is>
       </c>
       <c r="N128" t="inlineStr">
@@ -9464,7 +9464,7 @@
       </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>Clear SkyArk Space Station</t>
+          <t>Hoàn thành Trạm Không Gian SkyArk</t>
         </is>
       </c>
       <c r="N129" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 24 Sao</t>
+          <t>Nhận tổng cộng 24 Ngôi Sao.</t>
         </is>
       </c>
       <c r="N130" t="inlineStr">
@@ -9604,7 +9604,7 @@
       </c>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Nhận tổng cộng 72 Sao</t>
+          <t>Thu thập tổng cộng 72 Ngôi Sao</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -9674,7 +9674,7 @@
       </c>
       <c r="M132" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 2 với 3 Sao</t>
+          <t>Hoàn thành Đường Đua Dải Ngân Hà Vô Tận 2 với 3 Sao</t>
         </is>
       </c>
       <c r="N132" t="inlineStr">
@@ -9744,7 +9744,7 @@
       </c>
       <c r="M133" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 6 với 3 Sao</t>
+          <t>Hoàn thành Đường Đua Dải Ngân Hà Vô Tận 6 với 3 Sao</t>
         </is>
       </c>
       <c r="N133" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="M134" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 10 với 3 Sao</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 10 với 3 Sao</t>
         </is>
       </c>
       <c r="N134" t="inlineStr">
@@ -9884,7 +9884,7 @@
       </c>
       <c r="M135" t="inlineStr">
         <is>
-          <t>Hoàn thành Endless Galaxy Track 12 với 3 Sao</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 12 với 3 Sao</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
@@ -9954,7 +9954,7 @@
       </c>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Mở khóa tổng cộng 5 Persona Pinball</t>
+          <t>Mở khóa tổng cộng 5 Bóng Bi Nhân Cách</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -10024,7 +10024,7 @@
       </c>
       <c r="M137" t="inlineStr">
         <is>
-          <t>Mở khóa tổng cộng 10 Persona Pinball</t>
+          <t>Mở khóa tổng cộng 10 Bóng Cá Tính</t>
         </is>
       </c>
       <c r="N137" t="inlineStr">
@@ -10094,7 +10094,7 @@
       </c>
       <c r="M138" t="inlineStr">
         <is>
-          <t>Mở khóa tổng cộng 15 Persona Pinball</t>
+          <t>Mở khóa tổng cộng 15 Bàn Bida Nhân Cách</t>
         </is>
       </c>
       <c r="N138" t="inlineStr">
@@ -10164,7 +10164,7 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>Nhận 5 ROM Chiến Thuật Hạng S</t>
+          <t>Thu thập 5 ROM Chiến Thuật Hạng S</t>
         </is>
       </c>
       <c r="N139" t="inlineStr">
@@ -10234,7 +10234,7 @@
       </c>
       <c r="M140" t="inlineStr">
         <is>
-          <t>Nhận 10 ROM Chiến Thuật Hạng S</t>
+          <t>Thu thập 10 ROM Chiến Thuật hạng S</t>
         </is>
       </c>
       <c r="N140" t="inlineStr">
@@ -10304,7 +10304,7 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>Persona Pinball thực hiện Skills 50 lần</t>
+          <t>Thực Hiện Kỹ Năng Với Persona Pinball 50 Lần</t>
         </is>
       </c>
       <c r="N141" t="inlineStr">
@@ -10374,7 +10374,7 @@
       </c>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Persona Pinball thực hiện Rush 50 lần</t>
+          <t>Thực Hiện Rush Với Persona Pinball 50 Lần</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -10444,7 +10444,7 @@
       </c>
       <c r="M143" t="inlineStr">
         <is>
-          <t>Clear Endless Galaxy Track 2</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 2</t>
         </is>
       </c>
       <c r="N143" t="inlineStr">
@@ -10514,7 +10514,7 @@
       </c>
       <c r="M144" t="inlineStr">
         <is>
-          <t>Clear Endless Galaxy Track 6</t>
+          <t>Hoàn thành Đường Đua Dải Ngân Hà Vô Tận 6</t>
         </is>
       </c>
       <c r="N144" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="M145" t="inlineStr">
         <is>
-          <t>Clear Endless Galaxy Track 10</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 10</t>
         </is>
       </c>
       <c r="N145" t="inlineStr">
@@ -10654,7 +10654,7 @@
       </c>
       <c r="M146" t="inlineStr">
         <is>
-          <t>Clear Endless Galaxy Track 15</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 15</t>
         </is>
       </c>
       <c r="N146" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="M149" t="inlineStr">
         <is>
-          <t>Light Dagger</t>
+          <t>Dao Găm Ánh Sáng</t>
         </is>
       </c>
       <c r="N149" t="inlineStr">
@@ -10934,7 +10934,7 @@
       </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>Star Kiếm</t>
+          <t>Kiếm Sao</t>
         </is>
       </c>
       <c r="N150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="M151" t="inlineStr">
         <is>
-          <t>Bubble Blaster</t>
+          <t>Súng Bắn Bong Bóng</t>
         </is>
       </c>
       <c r="N151" t="inlineStr">
@@ -11074,7 +11074,7 @@
       </c>
       <c r="M152" t="inlineStr">
         <is>
-          <t>Laser Cannon</t>
+          <t>Pháo Laser</t>
         </is>
       </c>
       <c r="N152" t="inlineStr">
@@ -11144,7 +11144,7 @@
       </c>
       <c r="M153" t="inlineStr">
         <is>
-          <t>Aura Staff</t>
+          <t>Gậy Hồng Quang</t>
         </is>
       </c>
       <c r="N153" t="inlineStr">
@@ -11284,7 +11284,7 @@
       </c>
       <c r="M155" t="inlineStr">
         <is>
-          <t>C-Class Tactical ROM</t>
+          <t>Bản ROM Chiến Thuật Hạng C</t>
         </is>
       </c>
       <c r="N155" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>B-Class Tactical ROM</t>
+          <t>Bản ROM Chiến Thuật Hạng B</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
@@ -11424,7 +11424,7 @@
       </c>
       <c r="M157" t="inlineStr">
         <is>
-          <t>A-Class Tactical ROM</t>
+          <t>ROM Chiến Thuật Hạng A</t>
         </is>
       </c>
       <c r="N157" t="inlineStr">
@@ -11494,7 +11494,7 @@
       </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>S-Class Tactical ROM</t>
+          <t>ROM Chiến Thuật Hạng S</t>
         </is>
       </c>
       <c r="N158" t="inlineStr">
@@ -11634,7 +11634,7 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>Compare</t>
+          <t>So sánh</t>
         </is>
       </c>
       <c r="N160" t="inlineStr">
@@ -11704,7 +11704,7 @@
       </c>
       <c r="M161" t="inlineStr">
         <is>
-          <t>Switch</t>
+          <t>Chuyển đổi</t>
         </is>
       </c>
       <c r="N161" t="inlineStr">
@@ -11844,7 +11844,7 @@
       </c>
       <c r="M163" t="inlineStr">
         <is>
-          <t>Bộ ROM Chiến Thuật này đã được một Pinball trang bị</t>
+          <t>ROM Chiến thuật này đã được một Pinball trang bị rồi.</t>
         </is>
       </c>
       <c r="N163" t="inlineStr">
@@ -11914,7 +11914,7 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>Refraction Knife</t>
+          <t>Dao Khúc Xạ</t>
         </is>
       </c>
       <c r="N164" t="inlineStr">
@@ -11984,7 +11984,7 @@
       </c>
       <c r="M165" t="inlineStr">
         <is>
-          <t>Lumen Cutter</t>
+          <t>Lưỡi Kiếm Lumen</t>
         </is>
       </c>
       <c r="N165" t="inlineStr">
@@ -12054,7 +12054,7 @@
       </c>
       <c r="M166" t="inlineStr">
         <is>
-          <t>Dawnblade I</t>
+          <t>Kiếm Bình Minh I</t>
         </is>
       </c>
       <c r="N166" t="inlineStr">
@@ -12124,7 +12124,7 @@
       </c>
       <c r="M167" t="inlineStr">
         <is>
-          <t>Dawnblade II</t>
+          <t>Kiếm Bình Minh II</t>
         </is>
       </c>
       <c r="N167" t="inlineStr">
@@ -12194,7 +12194,7 @@
       </c>
       <c r="M168" t="inlineStr">
         <is>
-          <t>Dawnblade III</t>
+          <t>Kiếm Bình Minh III</t>
         </is>
       </c>
       <c r="N168" t="inlineStr">
@@ -12264,7 +12264,7 @@
       </c>
       <c r="M169" t="inlineStr">
         <is>
-          <t>Stellar Horizon I</t>
+          <t>Chân Trời Tinh Tú I</t>
         </is>
       </c>
       <c r="N169" t="inlineStr">
@@ -12334,7 +12334,7 @@
       </c>
       <c r="M170" t="inlineStr">
         <is>
-          <t>Stellar Horizon II</t>
+          <t>Chân Trời Tinh Tú II</t>
         </is>
       </c>
       <c r="N170" t="inlineStr">
@@ -12404,7 +12404,7 @@
       </c>
       <c r="M171" t="inlineStr">
         <is>
-          <t>Stellar Horizon III</t>
+          <t>Chân Trời Tinh Tú III</t>
         </is>
       </c>
       <c r="N171" t="inlineStr">
@@ -12544,7 +12544,7 @@
       </c>
       <c r="M173" t="inlineStr">
         <is>
-          <t>Starlane Longsword</t>
+          <t>Kiếm Dài Starlane</t>
         </is>
       </c>
       <c r="N173" t="inlineStr">
@@ -12614,7 +12614,7 @@
       </c>
       <c r="M174" t="inlineStr">
         <is>
-          <t>Galactic Judge I</t>
+          <t>Thẩm Phán Thiên Hà I</t>
         </is>
       </c>
       <c r="N174" t="inlineStr">
@@ -12684,7 +12684,7 @@
       </c>
       <c r="M175" t="inlineStr">
         <is>
-          <t>Galactic Judge II</t>
+          <t>Thẩm Phán Thiên Hà II</t>
         </is>
       </c>
       <c r="N175" t="inlineStr">
@@ -12754,7 +12754,7 @@
       </c>
       <c r="M176" t="inlineStr">
         <is>
-          <t>Galactic Judge III</t>
+          <t>Thẩm Phán Thiên Hà III</t>
         </is>
       </c>
       <c r="N176" t="inlineStr">
@@ -12824,7 +12824,7 @@
       </c>
       <c r="M177" t="inlineStr">
         <is>
-          <t>Cosmos Coda I</t>
+          <t>Hồi Kết Vũ Trụ I</t>
         </is>
       </c>
       <c r="N177" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="M178" t="inlineStr">
         <is>
-          <t>Cosmos Coda II</t>
+          <t>Hồi Kết Vũ Trụ II</t>
         </is>
       </c>
       <c r="N178" t="inlineStr">
@@ -12964,7 +12964,7 @@
       </c>
       <c r="M179" t="inlineStr">
         <is>
-          <t>Cosmos Coda III</t>
+          <t>Hồi Kết Vũ Trụ III</t>
         </is>
       </c>
       <c r="N179" t="inlineStr">
@@ -13034,7 +13034,7 @@
       </c>
       <c r="M180" t="inlineStr">
         <is>
-          <t>Compact Bubble Blaster</t>
+          <t>Súng Bong Bóng Cầm Tay</t>
         </is>
       </c>
       <c r="N180" t="inlineStr">
@@ -13104,7 +13104,7 @@
       </c>
       <c r="M181" t="inlineStr">
         <is>
-          <t>High-Pressure Star Launcher</t>
+          <t>Bệ Phóng Sao Áp Suất Cao</t>
         </is>
       </c>
       <c r="N181" t="inlineStr">
@@ -13174,7 +13174,7 @@
       </c>
       <c r="M182" t="inlineStr">
         <is>
-          <t>Aurora Sphere Generator I</t>
+          <t>Máy Tạo Quả Cầu Aurora I</t>
         </is>
       </c>
       <c r="N182" t="inlineStr">
@@ -13244,7 +13244,7 @@
       </c>
       <c r="M183" t="inlineStr">
         <is>
-          <t>Aurora Sphere Generator II</t>
+          <t>Máy Tạo Quả Cầu Aurora II</t>
         </is>
       </c>
       <c r="N183" t="inlineStr">
@@ -13314,7 +13314,7 @@
       </c>
       <c r="M184" t="inlineStr">
         <is>
-          <t>Aurora Sphere Generator III</t>
+          <t>Máy Tạo Quả Cầu Aurora III</t>
         </is>
       </c>
       <c r="N184" t="inlineStr">
@@ -13384,7 +13384,7 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>Starry Dreamland Booster I</t>
+          <t>Tăng Cường Giấc Mơ Sao I</t>
         </is>
       </c>
       <c r="N185" t="inlineStr">
@@ -13454,7 +13454,7 @@
       </c>
       <c r="M186" t="inlineStr">
         <is>
-          <t>Starry Dreamland Booster II</t>
+          <t>Tăng Cường Giấc Mơ Sao II</t>
         </is>
       </c>
       <c r="N186" t="inlineStr">
@@ -13524,7 +13524,7 @@
       </c>
       <c r="M187" t="inlineStr">
         <is>
-          <t>Starry Dreamland Booster III</t>
+          <t>Tăng Cường Giấc Mơ Sao III</t>
         </is>
       </c>
       <c r="N187" t="inlineStr">
@@ -13594,7 +13594,7 @@
       </c>
       <c r="M188" t="inlineStr">
         <is>
-          <t>Vintage Laser</t>
+          <t>Tia Laser Cổ Điển</t>
         </is>
       </c>
       <c r="N188" t="inlineStr">
@@ -13664,7 +13664,7 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>Stardock Laser Cannon</t>
+          <t>Pháo Laser Stardock</t>
         </is>
       </c>
       <c r="N189" t="inlineStr">
@@ -13734,7 +13734,7 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>Pulsar Impact I</t>
+          <t>Xung Kích Cấp I</t>
         </is>
       </c>
       <c r="N190" t="inlineStr">
@@ -13804,7 +13804,7 @@
       </c>
       <c r="M191" t="inlineStr">
         <is>
-          <t>Pulsar Impact II</t>
+          <t>Xung Kích Cấp II</t>
         </is>
       </c>
       <c r="N191" t="inlineStr">
@@ -13874,7 +13874,7 @@
       </c>
       <c r="M192" t="inlineStr">
         <is>
-          <t>Pulsar Impact III</t>
+          <t>Xung Kích Cấp III</t>
         </is>
       </c>
       <c r="N192" t="inlineStr">
@@ -13944,7 +13944,7 @@
       </c>
       <c r="M193" t="inlineStr">
         <is>
-          <t>Supernova Launch Array I</t>
+          <t>Mảng Phóng Tinh Vân Cấp I</t>
         </is>
       </c>
       <c r="N193" t="inlineStr">
@@ -14014,7 +14014,7 @@
       </c>
       <c r="M194" t="inlineStr">
         <is>
-          <t>Supernova Launch Array II</t>
+          <t>Mảng Phóng Tinh Vân Cấp II</t>
         </is>
       </c>
       <c r="N194" t="inlineStr">
@@ -14084,7 +14084,7 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>Supernova Launch Array III</t>
+          <t>Mảng Phóng Tinh Vân Cấp III</t>
         </is>
       </c>
       <c r="N195" t="inlineStr">
@@ -14154,7 +14154,7 @@
       </c>
       <c r="M196" t="inlineStr">
         <is>
-          <t>Drift Sensor Staff</t>
+          <t>Gậy Cảm biến Trôi dạt</t>
         </is>
       </c>
       <c r="N196" t="inlineStr">
@@ -14224,7 +14224,7 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>Interstellar Signpost</t>
+          <t>Biển Chỉ Dẫn Liên Sao</t>
         </is>
       </c>
       <c r="N197" t="inlineStr">
@@ -14294,7 +14294,7 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>Ancient Star Summoner I</t>
+          <t>Người Triệu Hoán Sao Cổ I</t>
         </is>
       </c>
       <c r="N198" t="inlineStr">
@@ -14364,7 +14364,7 @@
       </c>
       <c r="M199" t="inlineStr">
         <is>
-          <t>Ancient Star Summoner II</t>
+          <t>Người Triệu Hoán Sao Cổ II</t>
         </is>
       </c>
       <c r="N199" t="inlineStr">
@@ -14434,7 +14434,7 @@
       </c>
       <c r="M200" t="inlineStr">
         <is>
-          <t>Ancient Star Summoner III</t>
+          <t>Người Triệu Hoán Sao Cổ III</t>
         </is>
       </c>
       <c r="N200" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="M209" t="inlineStr">
         <is>
-          <t>Moongazer's Sigil</t>
+          <t>Ấn Nguyệt Khán</t>
         </is>
       </c>
       <c r="N209" t="inlineStr">
@@ -15344,7 +15344,7 @@
       </c>
       <c r="M213" t="inlineStr">
         <is>
-          <t>Starfield Calibrator</t>
+          <t>Điều Tần Sao Trời</t>
         </is>
       </c>
       <c r="N213" t="inlineStr">
@@ -15484,7 +15484,7 @@
       </c>
       <c r="M215" t="inlineStr">
         <is>
-          <t>Forged Dwarf Star</t>
+          <t>Ngôi Sao Lùn Đã Rèn</t>
         </is>
       </c>
       <c r="N215" t="inlineStr">
@@ -15624,7 +15624,7 @@
       </c>
       <c r="M217" t="inlineStr">
         <is>
-          <t>Everbright Polestar</t>
+          <t>Ngôi Sao Bắc Đẩu Vĩnh Hằng</t>
         </is>
       </c>
       <c r="N217" t="inlineStr">
@@ -15694,7 +15694,7 @@
       </c>
       <c r="M218" t="inlineStr">
         <is>
-          <t>Solsworn Ciphers</t>
+          <t>Mật Ngữ Solsworn</t>
         </is>
       </c>
       <c r="N218" t="inlineStr">
@@ -15764,7 +15764,7 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>Frostburn</t>
+          <t>Bỏng Sương</t>
         </is>
       </c>
       <c r="N219" t="inlineStr">
@@ -15904,7 +15904,7 @@
       </c>
       <c r="M221" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách</t>
+          <t>Hoàn thành Thử thách</t>
         </is>
       </c>
       <c r="N221" t="inlineStr">
@@ -15974,7 +15974,7 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>Thử thách kết thúc</t>
+          <t>Thử Thách Kết Thúc</t>
         </is>
       </c>
       <c r="N222" t="inlineStr">
@@ -16044,7 +16044,7 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>Thử lại</t>
+          <t>Thử Lại</t>
         </is>
       </c>
       <c r="N223" t="inlineStr">
@@ -16184,7 +16184,7 @@
       </c>
       <c r="M225" t="inlineStr">
         <is>
-          <t>Return</t>
+          <t>Quay lại</t>
         </is>
       </c>
       <c r="N225" t="inlineStr">
@@ -16254,7 +16254,7 @@
       </c>
       <c r="M226" t="inlineStr">
         <is>
-          <t>Statistics</t>
+          <t>Thống Kê</t>
         </is>
       </c>
       <c r="N226" t="inlineStr">
@@ -16394,7 +16394,7 @@
       </c>
       <c r="M228" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="N228" t="inlineStr">
@@ -16464,7 +16464,7 @@
       </c>
       <c r="M229" t="inlineStr">
         <is>
-          <t>Stats</t>
+          <t>Chỉ Số</t>
         </is>
       </c>
       <c r="N229" t="inlineStr">
@@ -16604,7 +16604,7 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>Pinball Info</t>
+          <t>Thông Tin Pinball</t>
         </is>
       </c>
       <c r="N231" t="inlineStr">
@@ -16674,7 +16674,7 @@
       </c>
       <c r="M232" t="inlineStr">
         <is>
-          <t>Thông tin giai đoạn</t>
+          <t>Thông Tin Giai Đoạn</t>
         </is>
       </c>
       <c r="N232" t="inlineStr">
@@ -16744,7 +16744,7 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>Sundering Strike</t>
+          <t>Đòn Phân Rã</t>
         </is>
       </c>
       <c r="N233" t="inlineStr">
@@ -16814,7 +16814,7 @@
       </c>
       <c r="M234" t="inlineStr">
         <is>
-          <t>Hypercube</t>
+          <t>Siêu Khối Lập Phương</t>
         </is>
       </c>
       <c r="N234" t="inlineStr">
@@ -16884,7 +16884,7 @@
       </c>
       <c r="M235" t="inlineStr">
         <is>
-          <t>Nét tài hoa</t>
+          <t>Nét Thiên Tài</t>
         </is>
       </c>
       <c r="N235" t="inlineStr">
@@ -16954,7 +16954,7 @@
       </c>
       <c r="M236" t="inlineStr">
         <is>
-          <t>Hellflare Overload</t>
+          <t>Quá Tải Lửa Địa Ngục</t>
         </is>
       </c>
       <c r="N236" t="inlineStr">
@@ -17094,7 +17094,7 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>Quadruple Time Steps</t>
+          <t>Bốn Bước Nhịp</t>
         </is>
       </c>
       <c r="N238" t="inlineStr">
@@ -17164,7 +17164,7 @@
       </c>
       <c r="M239" t="inlineStr">
         <is>
-          <t>Moon Domain</t>
+          <t>Vùng Đất Trăng</t>
         </is>
       </c>
       <c r="N239" t="inlineStr">
@@ -17234,7 +17234,7 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>Sight of Unraveling</t>
+          <t>Cảnh Tàn Phá</t>
         </is>
       </c>
       <c r="N240" t="inlineStr">
@@ -17304,7 +17304,7 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>Critical Protocol</t>
+          <t>Giao Thức Bạo Kích</t>
         </is>
       </c>
       <c r="N241" t="inlineStr">
@@ -17374,7 +17374,7 @@
       </c>
       <c r="M242" t="inlineStr">
         <is>
-          <t>Lynae-Style Palettes</t>
+          <t>Bảng Màu Kiểu Lynae</t>
         </is>
       </c>
       <c r="N242" t="inlineStr">
@@ -17444,7 +17444,7 @@
       </c>
       <c r="M243" t="inlineStr">
         <is>
-          <t>Dreamweaver's Banquet</t>
+          <t>Yến Tiệc Của Dreamweaver</t>
         </is>
       </c>
       <c r="N243" t="inlineStr">
@@ -17514,7 +17514,7 @@
       </c>
       <c r="M244" t="inlineStr">
         <is>
-          <t>Shared Voyage</t>
+          <t>Hành Trình Đồng Hành</t>
         </is>
       </c>
       <c r="N244" t="inlineStr">
@@ -17584,7 +17584,7 @@
       </c>
       <c r="M245" t="inlineStr">
         <is>
-          <t>Go</t>
+          <t>Đi thôi</t>
         </is>
       </c>
       <c r="N245" t="inlineStr">
@@ -17654,7 +17654,7 @@
       </c>
       <c r="M246" t="inlineStr">
         <is>
-          <t>Restoration Site</t>
+          <t>Địa Điểm Phục Hồi</t>
         </is>
       </c>
       <c r="N246" t="inlineStr">
@@ -17724,7 +17724,7 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>Vật liệu không đủ</t>
+          <t>Nguyên liệu không đủ.</t>
         </is>
       </c>
       <c r="N247" t="inlineStr">
@@ -17794,7 +17794,7 @@
       </c>
       <c r="M248" t="inlineStr">
         <is>
-          <t>Deliver Materials</t>
+          <t>Giao Vật Liệu</t>
         </is>
       </c>
       <c r="N248" t="inlineStr">
@@ -17864,7 +17864,7 @@
       </c>
       <c r="M249" t="inlineStr">
         <is>
-          <t>Trại căn cứ</t>
+          <t>Trại Chính</t>
         </is>
       </c>
       <c r="N249" t="inlineStr">
@@ -17934,7 +17934,7 @@
       </c>
       <c r="M250" t="inlineStr">
         <is>
-          <t>Insufficient Vật phẩm</t>
+          <t>Vật phẩm không đủ.</t>
         </is>
       </c>
       <c r="N250" t="inlineStr">
@@ -18004,7 +18004,7 @@
       </c>
       <c r="M251" t="inlineStr">
         <is>
-          <t>Deliver Vật phẩm</t>
+          <t>Giao Vật Phẩm</t>
         </is>
       </c>
       <c r="N251" t="inlineStr">
@@ -18074,7 +18074,7 @@
       </c>
       <c r="M252" t="inlineStr">
         <is>
-          <t>Base Camp Lv. 1</t>
+          <t>Trại Chính Cấp 1</t>
         </is>
       </c>
       <c r="N252" t="inlineStr">
@@ -18144,7 +18144,7 @@
       </c>
       <c r="M253" t="inlineStr">
         <is>
-          <t>Base Camp Lv. 2</t>
+          <t>Trại Chính Cấp 2</t>
         </is>
       </c>
       <c r="N253" t="inlineStr">
@@ -18214,7 +18214,7 @@
       </c>
       <c r="M254" t="inlineStr">
         <is>
-          <t>Base Camp Lv. 3</t>
+          <t>Trại Chính Cấp 3</t>
         </is>
       </c>
       <c r="N254" t="inlineStr">
@@ -18284,7 +18284,7 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>Base Camp Lv. 4</t>
+          <t>Trại Cơ Bản Cấp 4</t>
         </is>
       </c>
       <c r="N255" t="inlineStr">
@@ -18354,7 +18354,7 @@
       </c>
       <c r="M256" t="inlineStr">
         <is>
-          <t>Base Camp Lv. 5</t>
+          <t>Trại Cơ Bản Cấp 5</t>
         </is>
       </c>
       <c r="N256" t="inlineStr">
@@ -18424,7 +18424,7 @@
       </c>
       <c r="M257" t="inlineStr">
         <is>
-          <t>Silent Crag</t>
+          <t>Vách Đá Im Lìm</t>
         </is>
       </c>
       <c r="N257" t="inlineStr">
@@ -18494,7 +18494,7 @@
       </c>
       <c r="M258" t="inlineStr">
         <is>
-          <t>Sealed Fissure</t>
+          <t>Khe Nứt Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N258" t="inlineStr">
@@ -18564,7 +18564,7 @@
       </c>
       <c r="M259" t="inlineStr">
         <is>
-          <t>Dimmr Deep</t>
+          <t>Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N259" t="inlineStr">
@@ -18634,7 +18634,7 @@
       </c>
       <c r="M260" t="inlineStr">
         <is>
-          <t>Solisia Landing</t>
+          <t>Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N260" t="inlineStr">
@@ -18704,7 +18704,7 @@
       </c>
       <c r="M261" t="inlineStr">
         <is>
-          <t>Trại căn cứ</t>
+          <t>Trại Chính</t>
         </is>
       </c>
       <c r="N261" t="inlineStr">
@@ -18774,7 +18774,7 @@
       </c>
       <c r="M262" t="inlineStr">
         <is>
-          <t>Prism Fruit Spectrometer</t>
+          <t>Máy Phân Tích Sắc Cầu</t>
         </is>
       </c>
       <c r="N262" t="inlineStr">
@@ -18844,7 +18844,7 @@
       </c>
       <c r="M263" t="inlineStr">
         <is>
-          <t>Restoration</t>
+          <t>Phục Hồi</t>
         </is>
       </c>
       <c r="N263" t="inlineStr">
@@ -18914,7 +18914,7 @@
       </c>
       <c r="M264" t="inlineStr">
         <is>
-          <t>Hoàn thành tất cả hoạt động Phục hồi ở bất kỳ khu vực nào</t>
+          <t>Hoàn thành tất cả hoạt động Phục Hồi ở bất kỳ khu vực nào.</t>
         </is>
       </c>
       <c r="N264" t="inlineStr">
@@ -18984,7 +18984,7 @@
       </c>
       <c r="M265" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách tại Vách Đá Tĩnh Lặng</t>
+          <t>Hoàn thành thử thách tại Vách Đá Im Lặng</t>
         </is>
       </c>
       <c r="N265" t="inlineStr">
@@ -19054,7 +19054,7 @@
       </c>
       <c r="M266" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách tại Khe Nứt Bịt Kín</t>
+          <t>Hoàn thành thử thách tại Khe Nứt Bị Phong Ấn</t>
         </is>
       </c>
       <c r="N266" t="inlineStr">
@@ -19194,7 +19194,7 @@
       </c>
       <c r="M268" t="inlineStr">
         <is>
-          <t>Hoàn thành thử thách tại Bãi Đáp Solisia</t>
+          <t>Hoàn thành các thử thách tại Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N268" t="inlineStr">
@@ -19264,7 +19264,7 @@
       </c>
       <c r="M269" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Khu vực tại Vách Đá Tĩnh Lặng</t>
+          <t>Hoàn thành Nhiệm Vụ Khu Vực tại Vách Đá Im Lặng</t>
         </is>
       </c>
       <c r="N269" t="inlineStr">
@@ -19334,7 +19334,7 @@
       </c>
       <c r="M270" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Khu vực tại Khe Nứt Bịt Kín</t>
+          <t>Hoàn thành Nhiệm Vụ Khu Vực tại Khe Nứt Bị Phong Ấn</t>
         </is>
       </c>
       <c r="N270" t="inlineStr">
@@ -19404,7 +19404,7 @@
       </c>
       <c r="M271" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Khu vực tại Vực Sâu Dimmr</t>
+          <t>Hoàn thành Nhiệm Vụ Khu Vực tại Vực Sâu Dimmr</t>
         </is>
       </c>
       <c r="N271" t="inlineStr">
@@ -19474,7 +19474,7 @@
       </c>
       <c r="M272" t="inlineStr">
         <is>
-          <t>Hoàn thành Nhiệm vụ Khu vực tại Bãi Đáp Solisia</t>
+          <t>Hoàn thành Nhiệm Vụ Khu Vực tại Bến Đáp Solisia</t>
         </is>
       </c>
       <c r="N272" t="inlineStr">
@@ -19544,7 +19544,7 @@
       </c>
       <c r="M273" t="inlineStr">
         <is>
-          <t>Status</t>
+          <t>Trạng thái</t>
         </is>
       </c>
       <c r="N273" t="inlineStr">
@@ -19614,7 +19614,7 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>Restoring</t>
+          <t>Đang khôi phục...</t>
         </is>
       </c>
       <c r="N274" t="inlineStr">
@@ -19684,7 +19684,7 @@
       </c>
       <c r="M275" t="inlineStr">
         <is>
-          <t>Hoàn tất phục hồi</t>
+          <t>Hoàn Thành Phục Hồi</t>
         </is>
       </c>
       <c r="N275" t="inlineStr">
@@ -19754,7 +19754,7 @@
       </c>
       <c r="M276" t="inlineStr">
         <is>
-          <t>Restoration Materials</t>
+          <t>Vật Liệu Phục Hồi</t>
         </is>
       </c>
       <c r="N276" t="inlineStr">
@@ -19824,7 +19824,7 @@
       </c>
       <c r="M277" t="inlineStr">
         <is>
-          <t>Có thể Phục hồi</t>
+          <t>Có thể phục hồi</t>
         </is>
       </c>
       <c r="N277" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>Có thể khôi phục thêm Voidbane Eldertrees</t>
+          <t>Có thể khôi phục thêm nhiều Cây Già Voidbane nữa</t>
         </is>
       </c>
       <c r="N280" t="inlineStr">
@@ -20104,7 +20104,7 @@
       </c>
       <c r="M281" t="inlineStr">
         <is>
-          <t>Có thể giao thêm Prism Fruits</t>
+          <t>Có thể giao thêm Quả Cầu Lăng Kính</t>
         </is>
       </c>
       <c r="N281" t="inlineStr">
@@ -20174,7 +20174,7 @@
       </c>
       <c r="M282" t="inlineStr">
         <is>
-          <t>Silent Crag Treasure Spot</t>
+          <t>Kho Báu Vách Đá Vắng Lặng</t>
         </is>
       </c>
       <c r="N282" t="inlineStr">
@@ -20244,7 +20244,7 @@
       </c>
       <c r="M283" t="inlineStr">
         <is>
-          <t>Thử thách Light Builder tại Silent Crag</t>
+          <t>Thử Thách Người Dựng Ánh Sáng Vách Đá Vắng Lặng</t>
         </is>
       </c>
       <c r="N283" t="inlineStr">
@@ -20314,7 +20314,7 @@
       </c>
       <c r="M284" t="inlineStr">
         <is>
-          <t>Sealed Fissure Treasure Spot</t>
+          <t>Điểm Kho Báu Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N284" t="inlineStr">
@@ -20384,7 +20384,7 @@
       </c>
       <c r="M285" t="inlineStr">
         <is>
-          <t>Thử thách Light Builder tại Sealed Fissure</t>
+          <t>Thử Thách Kiến Tạo Ánh Sáng Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N285" t="inlineStr">
@@ -20454,7 +20454,7 @@
       </c>
       <c r="M286" t="inlineStr">
         <is>
-          <t>Sealed Fissure Void Storm Zone</t>
+          <t>Khu Vực Bão Hư Không Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N286" t="inlineStr">
@@ -20524,7 +20524,7 @@
       </c>
       <c r="M287" t="inlineStr">
         <is>
-          <t>Sealed Fissure Lahai-Roi Blocks</t>
+          <t>Khối Lahai-Roi Đã Niêm Phong</t>
         </is>
       </c>
       <c r="N287" t="inlineStr">
@@ -20594,7 +20594,7 @@
       </c>
       <c r="M288" t="inlineStr">
         <is>
-          <t>Dimmr Deep Treasure Spot</t>
+          <t>Điểm Kho Báu Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N288" t="inlineStr">
@@ -20664,7 +20664,7 @@
       </c>
       <c r="M289" t="inlineStr">
         <is>
-          <t>Thử thách Light Builder tại Dimmr Deep</t>
+          <t>Thử Thách Kiến Tạo Ánh Sáng Vực Sâu Mờ Mịt</t>
         </is>
       </c>
       <c r="N289" t="inlineStr">
@@ -20734,7 +20734,7 @@
       </c>
       <c r="M290" t="inlineStr">
         <is>
-          <t>Nhiệm vụ Thám hiểm "Trái tim Dimmr tan vỡ"</t>
+          <t>Nhiệm Vụ Thám Hiểm "Trái Tim Dimmr Vỡ Nát"</t>
         </is>
       </c>
       <c r="N290" t="inlineStr">
@@ -20804,7 +20804,7 @@
       </c>
       <c r="M291" t="inlineStr">
         <is>
-          <t>Solisia Landing Treasure Spot</t>
+          <t>Điểm Kho Báu Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N291" t="inlineStr">
@@ -20874,7 +20874,7 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>Thử thách Light Builder tại Solisia Landing</t>
+          <t>Thử Thách Kiến Tạo Ánh Sáng Bãi Đáp Solisia</t>
         </is>
       </c>
       <c r="N292" t="inlineStr">
@@ -20944,7 +20944,7 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>Vào vùng Đất Nghịch Lý</t>
+          <t>Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N293" t="inlineStr">
@@ -21014,7 +21014,7 @@
       </c>
       <c r="M294" t="inlineStr">
         <is>
-          <t>Dimmr Plains Survey</t>
+          <t>Khảo Sát Đồng Bằng Dimmr</t>
         </is>
       </c>
       <c r="N294" t="inlineStr">
@@ -21084,7 +21084,7 @@
       </c>
       <c r="M295" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Vào vùng Đất Nghịch Lý</t>
+          <t>Không tìm thấy cấu hình cho Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N295" t="inlineStr">
@@ -21154,7 +21154,7 @@
       </c>
       <c r="M296" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Vào vùng Đất Nghịch Lý</t>
+          <t>Không tìm thấy cấu hình cho Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N296" t="inlineStr">
@@ -21224,7 +21224,7 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>Không tìm thấy cấu hình Vào vùng Đất Nghịch Lý</t>
+          <t>Không tìm thấy cấu hình cho Vào Vùng Đất Nghịch Lý</t>
         </is>
       </c>
       <c r="N297" t="inlineStr">
@@ -21364,7 +21364,7 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>Trại Cơ bản đã đạt cấp tối đa</t>
+          <t>Trại Cơ Bản đã đạt cấp tối đa</t>
         </is>
       </c>
       <c r="N299" t="inlineStr">
@@ -21434,7 +21434,7 @@
       </c>
       <c r="M300" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện nâng cấp Trại Cơ bản</t>
+          <t>Chưa đủ điều kiện nâng cấp Trại Cơ Bản</t>
         </is>
       </c>
       <c r="N300" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="M301" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện nâng cấp Trại Cơ bản</t>
+          <t>Chưa đủ điều kiện nâng cấp Trại Cơ Bản</t>
         </is>
       </c>
       <c r="N301" t="inlineStr">
@@ -21574,7 +21574,7 @@
       </c>
       <c r="M302" t="inlineStr">
         <is>
-          <t>Voidbane Eldertree hiện không thể khôi phục</t>
+          <t>Cây Già Diệt Hư không thể phục hồi trong trạng thái hiện tại</t>
         </is>
       </c>
       <c r="N302" t="inlineStr">
@@ -21644,7 +21644,7 @@
       </c>
       <c r="M303" t="inlineStr">
         <is>
-          <t>Hiện không thể nâng cấp Trại Cơ bản</t>
+          <t>Không thể nâng cấp Trại Cơ Bản lúc này</t>
         </is>
       </c>
       <c r="N303" t="inlineStr">
@@ -21714,7 +21714,7 @@
       </c>
       <c r="M304" t="inlineStr">
         <is>
-          <t>Chưa đủ điều kiện khôi phục Voidbane Eldertree</t>
+          <t>Điều kiện phục hồi Cây Già Diệt Hư chưa đủ</t>
         </is>
       </c>
       <c r="N304" t="inlineStr">
@@ -21784,7 +21784,7 @@
       </c>
       <c r="M305" t="inlineStr">
         <is>
-          <t>Sự kiện Vào vùng Đất Nghịch Lý chưa mở</t>
+          <t>Sự kiện Vào Vùng Đất Nghịch Lý chưa mở</t>
         </is>
       </c>
       <c r="N305" t="inlineStr">
@@ -21994,7 +21994,7 @@
       </c>
       <c r="M308" t="inlineStr">
         <is>
-          <t>Không thể chuyển đổi trong Chế độ Co-op</t>
+          <t>Không thể chuyển đổi trong Chế Độ Hợp Tác</t>
         </is>
       </c>
       <c r="N308" t="inlineStr">
@@ -22064,7 +22064,7 @@
       </c>
       <c r="M309" t="inlineStr">
         <is>
-          <t>Không tồn tại cấu hình nhiệm vụ</t>
+          <t>Cấu hình nhiệm vụ không tồn tại.</t>
         </is>
       </c>
       <c r="N309" t="inlineStr">
@@ -22134,7 +22134,7 @@
       </c>
       <c r="M310" t="inlineStr">
         <is>
-          <t>Vật phẩm này đã được nhận</t>
+          <t>Vật phẩm này đã được nhận rồi.</t>
         </is>
       </c>
       <c r="N310" t="inlineStr">
@@ -22274,7 +22274,7 @@
       </c>
       <c r="M312" t="inlineStr">
         <is>
-          <t>Không thể nhận được vật phẩm tương ứng</t>
+          <t>Không thể nhận vật phẩm tương ứng</t>
         </is>
       </c>
       <c r="N312" t="inlineStr">
@@ -22414,7 +22414,7 @@
       </c>
       <c r="M314" t="inlineStr">
         <is>
-          <t>Chưa nhận thưởng</t>
+          <t>Chưa nhận phần thưởng</t>
         </is>
       </c>
       <c r="N314" t="inlineStr">
@@ -22554,7 +22554,7 @@
       </c>
       <c r="M316" t="inlineStr">
         <is>
-          <t>"Into the Land of Paradox" event</t>
+          <t>"Sự kiện "Vào Vùng Đất Nghịch Lý""</t>
         </is>
       </c>
       <c r="N316" t="inlineStr">
@@ -22624,7 +22624,7 @@
       </c>
       <c r="M317" t="inlineStr">
         <is>
-          <t>Giải pháp Ánh sáng cho Bóng tối</t>
+          <t>Quyết Tâm Soi Sáng Bóng Tối</t>
         </is>
       </c>
       <c r="N317" t="inlineStr">
@@ -22764,7 +22764,7 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>Khi Rune Lấp Lánh</t>
+          <t>Khi Những Rune Lấp Lánh</t>
         </is>
       </c>
       <c r="N319" t="inlineStr">
@@ -22834,7 +22834,7 @@
       </c>
       <c r="M320" t="inlineStr">
         <is>
-          <t>Solsworn Ciphers</t>
+          <t>Mật Ngữ Solsworn</t>
         </is>
       </c>
       <c r="N320" t="inlineStr">
@@ -22904,7 +22904,7 @@
       </c>
       <c r="M321" t="inlineStr">
         <is>
-          <t>Absolute Pulsation</t>
+          <t>Rung Động Tuyệt Đối</t>
         </is>
       </c>
       <c r="N321" t="inlineStr">
@@ -23044,7 +23044,7 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>Solsworn Ciphers</t>
+          <t>Mật Ngữ Solsworn</t>
         </is>
       </c>
       <c r="N323" t="inlineStr">
@@ -23114,7 +23114,7 @@
       </c>
       <c r="M324" t="inlineStr">
         <is>
-          <t>Chương III Màn IV: "Vàng lơ lửng trong bóng tối"</t>
+          <t>Chương III Cảnh IV: "Vàng trôi trong bóng tối"</t>
         </is>
       </c>
       <c r="N324" t="inlineStr">
@@ -23184,7 +23184,7 @@
       </c>
       <c r="M325" t="inlineStr">
         <is>
-          <t>Chuyển cảnh: Hậu trường "Thỏ phản chiếu trong sắc tối"</t>
+          <t>Chuyển cảnh: Ngoại truyện "Hình Bóng Thỏ Trong Kính Râm"</t>
         </is>
       </c>
       <c r="N325" t="inlineStr">
@@ -23324,7 +23324,7 @@
       </c>
       <c r="M327" t="inlineStr">
         <is>
-          <t>Thỏ phản chiếu trong Bóng tối</t>
+          <t>Rabbit Phản Chiếu Trong Kính</t>
         </is>
       </c>
       <c r="N327" t="inlineStr">
@@ -23394,7 +23394,7 @@
       </c>
       <c r="M328" t="inlineStr">
         <is>
-          <t>Bay theo nhịp điệu</t>
+          <t>Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N328" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="M330" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N330" t="inlineStr">
@@ -23674,7 +23674,7 @@
       </c>
       <c r="M332" t="inlineStr">
         <is>
-          <t>Endstate Matrix: Doomsday Cycle</t>
+          <t>Ma Trận Tận Thế: Vòng Luân Hồi Ngày Tận Thế</t>
         </is>
       </c>
       <c r="N332" t="inlineStr">
@@ -23744,7 +23744,7 @@
       </c>
       <c r="M333" t="inlineStr">
         <is>
-          <t>Quà tặng của Solsworn</t>
+          <t>Quà Tặng Của Solsworn</t>
         </is>
       </c>
       <c r="N333" t="inlineStr">
@@ -23814,7 +23814,7 @@
       </c>
       <c r="M334" t="inlineStr">
         <is>
-          <t>Màu Đỏ Rực Cháy Trong Ký Ức</t>
+          <t>Lửa Đỏ Trong Ký Ức</t>
         </is>
       </c>
       <c r="N334" t="inlineStr">
@@ -23884,7 +23884,7 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>Bay theo nhịp điệu</t>
+          <t>Bay theo Nhịp Điệu</t>
         </is>
       </c>
       <c r="N335" t="inlineStr">
@@ -24024,7 +24024,7 @@
       </c>
       <c r="M337" t="inlineStr">
         <is>
-          <t>Hiệp sĩ Hoang dã</t>
+          <t>Hiệp Sĩ Hoang Dã</t>
         </is>
       </c>
       <c r="N337" t="inlineStr">
@@ -24164,7 +24164,7 @@
       </c>
       <c r="M339" t="inlineStr">
         <is>
-          <t>Endstate Matrix: Doomsday Cycle</t>
+          <t>Ma Trận Tận Thế: Vòng Luân Hồi Ngày Tận Thế</t>
         </is>
       </c>
       <c r="N339" t="inlineStr">
@@ -24234,7 +24234,7 @@
       </c>
       <c r="M340" t="inlineStr">
         <is>
-          <t>Gifts of Solsworn</t>
+          <t>Quà Tặng Của Solsworn</t>
         </is>
       </c>
       <c r="N340" t="inlineStr">
@@ -24304,7 +24304,7 @@
       </c>
       <c r="M341" t="inlineStr">
         <is>
-          <t>Màu Đỏ Rực Cháy Trong Ký Ức</t>
+          <t>Lửa Đỏ Trong Ký Ức</t>
         </is>
       </c>
       <c r="N341" t="inlineStr">
@@ -24374,7 +24374,7 @@
       </c>
       <c r="M342" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N342" t="inlineStr">
@@ -24444,7 +24444,7 @@
       </c>
       <c r="M343" t="inlineStr">
         <is>
-          <t>Vehicle Looks</t>
+          <t>Ngoại Hình Phương Tiện</t>
         </is>
       </c>
       <c r="N343" t="inlineStr">
@@ -24514,7 +24514,7 @@
       </c>
       <c r="M344" t="inlineStr">
         <is>
-          <t>Echo Management Optimization</t>
+          <t>Tối Ưu Hóa Quản Lý</t>
         </is>
       </c>
       <c r="N344" t="inlineStr">
@@ -24584,7 +24584,7 @@
       </c>
       <c r="M345" t="inlineStr">
         <is>
-          <t>Loại bỏ Echo thông minh</t>
+          <t>Loại Bỏ Hồi Âm Thông Minh</t>
         </is>
       </c>
       <c r="N345" t="inlineStr">
@@ -24654,7 +24654,7 @@
       </c>
       <c r="M346" t="inlineStr">
         <is>
-          <t>Echo Management Optimization</t>
+          <t>Tối Ưu Hóa Quản Lý</t>
         </is>
       </c>
       <c r="N346" t="inlineStr">
@@ -24724,7 +24724,7 @@
       </c>
       <c r="M347" t="inlineStr">
         <is>
-          <t>Loại bỏ Echo thông minh</t>
+          <t>Loại Bỏ Hồi Âm Thông Minh</t>
         </is>
       </c>
       <c r="N347" t="inlineStr">
@@ -24794,7 +24794,7 @@
       </c>
       <c r="M348" t="inlineStr">
         <is>
-          <t>Dùng Hiyuki để vượt Tháp Nguy hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch cảnh: Khu vực Nguy hiểm</t>
+          <t>Dùng Hiyuki để vượt Tháp Nguy Hiểm từ Tầng 1 đến Tầng 4 trong "Tháp Nghịch Cảnh: Khu Nguy Hiểm".</t>
         </is>
       </c>
       <c r="N348" t="inlineStr">
@@ -24864,7 +24864,7 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>Dùng Denia để vượt Tháp Nguy hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch cảnh: Khu vực Nguy hiểm</t>
+          <t>Dùng Denia vượt qua Tháp Hazard từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N349" t="inlineStr">
@@ -24934,7 +24934,7 @@
       </c>
       <c r="M350" t="inlineStr">
         <is>
-          <t>Dùng Aemeath để vượt Tháp Nguy hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch cảnh: Khu vực Nguy hiểm</t>
+          <t>Dùng Aemeath để vượt Tháp Hazard từ Tầng 1 đến Tầng 4 trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N350" t="inlineStr">
@@ -25004,7 +25004,7 @@
       </c>
       <c r="M351" t="inlineStr">
         <is>
-          <t>Dùng Sigrika để vượt Tháp Nguy hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch cảnh: Khu vực Nguy hiểm</t>
+          <t>Dùng Sigrika để vượt tầng 1 đến tầng 4 của Hazard Tower trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N351" t="inlineStr">
@@ -25074,7 +25074,7 @@
       </c>
       <c r="M352" t="inlineStr">
         <is>
-          <t>Dùng Cartethyia để vượt Tháp Nguy hiểm Tầng 1 đến Tầng 4 trong Tháp Nghịch cảnh: Khu vực Nguy hiểm</t>
+          <t>Dùng Cartethyia để vượt từ tầng 1 đến tầng 4 của Tháp Nguy Hiểm trong Tower of Adversity: Hazard Zone</t>
         </is>
       </c>
       <c r="N352" t="inlineStr">
@@ -25144,7 +25144,7 @@
       </c>
       <c r="M353" t="inlineStr">
         <is>
-          <t>Dùng Hiyuki để vượt Vùng nước Hồi sinh: Dòng chảy ở Vùng đất Than thở</t>
+          <t>Dùng Hiyuki để vượt "Nước Tái Sinh: Dòng Chảy Cuồng Nộ" ở Whimpering Wastes.</t>
         </is>
       </c>
       <c r="N353" t="inlineStr">
@@ -25214,7 +25214,7 @@
       </c>
       <c r="M354" t="inlineStr">
         <is>
-          <t>Sử dụng Denia để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Denia để dọn sạch Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N354" t="inlineStr">
@@ -25284,7 +25284,7 @@
       </c>
       <c r="M355" t="inlineStr">
         <is>
-          <t>Sử dụng Aemeath hoặc Luuk Herssen để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Aemeath hoặc Luuk Herssen để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N355" t="inlineStr">
@@ -25354,7 +25354,7 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>Sử dụng Sigrika hoặc Phrolova để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Sigrika hoặc Phrolova để vượt ải Respawning Waters: Torrents ở Whimpering Wastes</t>
         </is>
       </c>
       <c r="N356" t="inlineStr">
@@ -25424,7 +25424,7 @@
       </c>
       <c r="M357" t="inlineStr">
         <is>
-          <t>Sử dụng Augusta hoặc Cartethyia để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
+          <t>Dùng Augusta hoặc Cartethyia để vượt ải Respawning Waters: Torrents tại Whimpering Wastes</t>
         </is>
       </c>
       <c r="N357" t="inlineStr">
@@ -25494,7 +25494,7 @@
       </c>
       <c r="M358" t="inlineStr">
         <is>
-          <t>Vượt ải thử thách Voidwing Moth tại Pioneer Training Ground</t>
+          <t>Hoàn thành thử thách đối đầu Voidwing Moth tại Pioneer Training Ground</t>
         </is>
       </c>
       <c r="N358" t="inlineStr">
@@ -25564,7 +25564,7 @@
       </c>
       <c r="M359" t="inlineStr">
         <is>
-          <t>Vượt ải Honami City Giai đoạn 4 trong sự kiện "Star Bouncing"</t>
+          <t>Hoàn thành Giai đoạn 4 Honami City trong sự kiện "Star Bouncing"</t>
         </is>
       </c>
       <c r="N359" t="inlineStr">
@@ -25634,7 +25634,7 @@
       </c>
       <c r="M360" t="inlineStr">
         <is>
-          <t>Vượt ải Endless Galaxy Track 10 trong sự kiện "Star Bouncing"</t>
+          <t>Hoàn thành Đường Đua Endless Galaxy 10 trong sự kiện "Star Bouncing"</t>
         </is>
       </c>
       <c r="N360" t="inlineStr">
@@ -25704,7 +25704,7 @@
       </c>
       <c r="M361" t="inlineStr">
         <is>
-          <t>Mặt Trời Rực Cháy trong Rừng</t>
+          <t>Mặt Trời Nóng Rực Trong Khu Rừng</t>
         </is>
       </c>
       <c r="N361" t="inlineStr">
@@ -25774,7 +25774,7 @@
       </c>
       <c r="M362" t="inlineStr">
         <is>
-          <t>Undersea Flame</t>
+          <t>Lửa Dưới Biển</t>
         </is>
       </c>
       <c r="N362" t="inlineStr">
@@ -25844,7 +25844,7 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>Withering Dream</t>
+          <t>Giấc Mơ Tàn Úa</t>
         </is>
       </c>
       <c r="N363" t="inlineStr">
@@ -25914,7 +25914,7 @@
       </c>
       <c r="M364" t="inlineStr">
         <is>
-          <t>Gale Canvas</t>
+          <t>Bức Tranh Gió</t>
         </is>
       </c>
       <c r="N364" t="inlineStr">
@@ -25984,7 +25984,7 @@
       </c>
       <c r="M365" t="inlineStr">
         <is>
-          <t>Jade Buckle</t>
+          <t>Móc Jade</t>
         </is>
       </c>
       <c r="N365" t="inlineStr">
@@ -26054,7 +26054,7 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>The Lament Epoch</t>
+          <t>Kỷ Nguyên Than Khóc</t>
         </is>
       </c>
       <c r="N366" t="inlineStr">
@@ -26124,7 +26124,7 @@
       </c>
       <c r="M367" t="inlineStr">
         <is>
-          <t>Cardiotonic</t>
+          <t>Thuốc Tăng Cường Tim</t>
         </is>
       </c>
       <c r="N367" t="inlineStr">
@@ -26194,7 +26194,7 @@
       </c>
       <c r="M368" t="inlineStr">
         <is>
-          <t>Nameplate</t>
+          <t>Bảng tên</t>
         </is>
       </c>
       <c r="N368" t="inlineStr">
@@ -26264,7 +26264,7 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>Unordered Cube</t>
+          <t>Khối Lập Phương Lộn Xộn</t>
         </is>
       </c>
       <c r="N369" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>Super Mutated Sample</t>
+          <t>Mẫu Đột Biến Cấp Siêu</t>
         </is>
       </c>
       <c r="N370" t="inlineStr">
@@ -26404,7 +26404,7 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>Trái Tim Lửa</t>
+          <t>Trái Tim Hòa Quyện</t>
         </is>
       </c>
       <c r="N371" t="inlineStr">
@@ -26474,7 +26474,7 @@
       </c>
       <c r="M372" t="inlineStr">
         <is>
-          <t>Blistering Gemstone</t>
+          <t>Đá Quý Rực Lửa</t>
         </is>
       </c>
       <c r="N372" t="inlineStr">
@@ -26544,7 +26544,7 @@
       </c>
       <c r="M373" t="inlineStr">
         <is>
-          <t>Mobile Combat Boots</t>
+          <t>Giày Chiến Đấu Cơ Động</t>
         </is>
       </c>
       <c r="N373" t="inlineStr">
@@ -26614,7 +26614,7 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>Radiant Hope</t>
+          <t>Hy Vọng Rạng Ngời</t>
         </is>
       </c>
       <c r="N374" t="inlineStr">
@@ -26684,7 +26684,7 @@
       </c>
       <c r="M375" t="inlineStr">
         <is>
-          <t>Blood Debt</t>
+          <t>Món nợ máu</t>
         </is>
       </c>
       <c r="N375" t="inlineStr">
@@ -26754,7 +26754,7 @@
       </c>
       <c r="M376" t="inlineStr">
         <is>
-          <t>Bạc của Kẻ Hủy Diệt</t>
+          <t>Bạc Của Kẻ Hủy Diệt</t>
         </is>
       </c>
       <c r="N376" t="inlineStr">
@@ -26824,7 +26824,7 @@
       </c>
       <c r="M377" t="inlineStr">
         <is>
-          <t>Boxing Gloves</t>
+          <t>Găng Tay Quyền Anh</t>
         </is>
       </c>
       <c r="N377" t="inlineStr">
@@ -26894,7 +26894,7 @@
       </c>
       <c r="M378" t="inlineStr">
         <is>
-          <t>Prosthetic Blade</t>
+          <t>Lưỡi Kiếm Giả</t>
         </is>
       </c>
       <c r="N378" t="inlineStr">
@@ -26964,7 +26964,7 @@
       </c>
       <c r="M379" t="inlineStr">
         <is>
-          <t>Risky Game</t>
+          <t>Trò chơi mạo hiểm</t>
         </is>
       </c>
       <c r="N379" t="inlineStr">
@@ -27034,7 +27034,7 @@
       </c>
       <c r="M380" t="inlineStr">
         <is>
-          <t>Tactical Knife</t>
+          <t>Dao Chiến Thuật</t>
         </is>
       </c>
       <c r="N380" t="inlineStr">
@@ -27174,7 +27174,7 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>Crude Nameplate</t>
+          <t>Bảng Tên Thô</t>
         </is>
       </c>
       <c r="N382" t="inlineStr">
@@ -27244,7 +27244,7 @@
       </c>
       <c r="M383" t="inlineStr">
         <is>
-          <t>Eternal Sun</t>
+          <t>Mặt Trời Vĩnh Cửu</t>
         </is>
       </c>
       <c r="N383" t="inlineStr">
@@ -27384,7 +27384,7 @@
       </c>
       <c r="M385" t="inlineStr">
         <is>
-          <t>Old Device I</t>
+          <t>Thiết Bị Cũ I</t>
         </is>
       </c>
       <c r="N385" t="inlineStr">
@@ -27454,7 +27454,7 @@
       </c>
       <c r="M386" t="inlineStr">
         <is>
-          <t>Final Barrier</t>
+          <t>Rào Chắn Cuối Cùng</t>
         </is>
       </c>
       <c r="N386" t="inlineStr">
@@ -27524,7 +27524,7 @@
       </c>
       <c r="M387" t="inlineStr">
         <is>
-          <t>Resounding Bell</t>
+          <t>Chuông Vang Dội</t>
         </is>
       </c>
       <c r="N387" t="inlineStr">
@@ -27664,7 +27664,7 @@
       </c>
       <c r="M389" t="inlineStr">
         <is>
-          <t>Cautious Scarab</t>
+          <t>Bọ Cánh Cứng Thận Trọng</t>
         </is>
       </c>
       <c r="N389" t="inlineStr">
@@ -27734,7 +27734,7 @@
       </c>
       <c r="M390" t="inlineStr">
         <is>
-          <t>Watcher's Promise</t>
+          <t>Lời Hứa Của Giám Thị</t>
         </is>
       </c>
       <c r="N390" t="inlineStr">
@@ -27874,7 +27874,7 @@
       </c>
       <c r="M392" t="inlineStr">
         <is>
-          <t>Resilient Warcrab</t>
+          <t>Cua Chiến Kiên Cường</t>
         </is>
       </c>
       <c r="N392" t="inlineStr">
@@ -27944,7 +27944,7 @@
       </c>
       <c r="M393" t="inlineStr">
         <is>
-          <t>Blooming Snow</t>
+          <t>Tuyết Hoa Nở Rộ</t>
         </is>
       </c>
       <c r="N393" t="inlineStr">
@@ -28014,7 +28014,7 @@
       </c>
       <c r="M394" t="inlineStr">
         <is>
-          <t>Zephyr Canvas</t>
+          <t>Vải Zephyr</t>
         </is>
       </c>
       <c r="N394" t="inlineStr">
@@ -28084,7 +28084,7 @@
       </c>
       <c r="M395" t="inlineStr">
         <is>
-          <t>Perfect Crystal Shrimp</t>
+          <t>Tôm Thủy Tinh Hoàn Hảo</t>
         </is>
       </c>
       <c r="N395" t="inlineStr">
@@ -28154,7 +28154,7 @@
       </c>
       <c r="M396" t="inlineStr">
         <is>
-          <t>Aromatherapy</t>
+          <t>Liệu pháp hương thơm</t>
         </is>
       </c>
       <c r="N396" t="inlineStr">
@@ -28224,7 +28224,7 @@
       </c>
       <c r="M397" t="inlineStr">
         <is>
-          <t>Tacet Field Survival Guide</t>
+          <t>Hướng Dẫn Sinh Tồn Trong Tổ Tacet</t>
         </is>
       </c>
       <c r="N397" t="inlineStr">
@@ -28294,7 +28294,7 @@
       </c>
       <c r="M398" t="inlineStr">
         <is>
-          <t>Alloy Conch</t>
+          <t>Ốc Hợp Kim</t>
         </is>
       </c>
       <c r="N398" t="inlineStr">
@@ -28364,7 +28364,7 @@
       </c>
       <c r="M399" t="inlineStr">
         <is>
-          <t>Riot Shield</t>
+          <t>Khiên Bạo Loạn</t>
         </is>
       </c>
       <c r="N399" t="inlineStr">
@@ -28434,7 +28434,7 @@
       </c>
       <c r="M400" t="inlineStr">
         <is>
-          <t>Emergency Call</t>
+          <t>Cuộc Gọi Khẩn Cấp</t>
         </is>
       </c>
       <c r="N400" t="inlineStr">
@@ -28504,7 +28504,7 @@
       </c>
       <c r="M401" t="inlineStr">
         <is>
-          <t>Rapid Grapple</t>
+          <t>Túm Nhanh</t>
         </is>
       </c>
       <c r="N401" t="inlineStr">
@@ -28574,7 +28574,7 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>Aftersound Conch</t>
+          <t>Ốc Dư Âm</t>
         </is>
       </c>
       <c r="N402" t="inlineStr">
@@ -28644,7 +28644,7 @@
       </c>
       <c r="M403" t="inlineStr">
         <is>
-          <t>Juicy Pinecone</t>
+          <t>Quả thông mọng nước</t>
         </is>
       </c>
       <c r="N403" t="inlineStr">
@@ -28714,7 +28714,7 @@
       </c>
       <c r="M404" t="inlineStr">
         <is>
-          <t>"Mercy"</t>
+          <t>"Lòng thương xót"</t>
         </is>
       </c>
       <c r="N404" t="inlineStr">
@@ -28784,7 +28784,7 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>Infinite Cloud</t>
+          <t>Vân Vô Biên</t>
         </is>
       </c>
       <c r="N405" t="inlineStr">
@@ -28854,7 +28854,7 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>Energy Drink</t>
+          <t>Nước Tăng Lực</t>
         </is>
       </c>
       <c r="N406" t="inlineStr">
@@ -28924,7 +28924,7 @@
       </c>
       <c r="M407" t="inlineStr">
         <is>
-          <t>Molting Slough</t>
+          <t>Lột Xác</t>
         </is>
       </c>
       <c r="N407" t="inlineStr">
@@ -28994,7 +28994,7 @@
       </c>
       <c r="M408" t="inlineStr">
         <is>
-          <t>Siphoning Claw</t>
+          <t>Vuốt Hút Năng Lượng</t>
         </is>
       </c>
       <c r="N408" t="inlineStr">
@@ -29064,7 +29064,7 @@
       </c>
       <c r="M409" t="inlineStr">
         <is>
-          <t>Chìa Khóa Bình Yên</t>
+          <t>Chìa Khóa Thanh Bình</t>
         </is>
       </c>
       <c r="N409" t="inlineStr">
@@ -29134,7 +29134,7 @@
       </c>
       <c r="M410" t="inlineStr">
         <is>
-          <t>Sports Cookie</t>
+          <t>Bánh Quy Thể Thao</t>
         </is>
       </c>
       <c r="N410" t="inlineStr">
@@ -29204,7 +29204,7 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>Pha Lê Mâu Thuẫn</t>
+          <t>Pha Lê Nghịch Lý</t>
         </is>
       </c>
       <c r="N411" t="inlineStr">
@@ -29274,7 +29274,7 @@
       </c>
       <c r="M412" t="inlineStr">
         <is>
-          <t>The World</t>
+          <t>Thế Giới</t>
         </is>
       </c>
       <c r="N412" t="inlineStr">
@@ -29344,7 +29344,7 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>Dusty Grimoire</t>
+          <t>Cuốn Cổ Ngữ Bám Bụi</t>
         </is>
       </c>
       <c r="N413" t="inlineStr">
@@ -29414,7 +29414,7 @@
       </c>
       <c r="M414" t="inlineStr">
         <is>
-          <t>Tacetite Bloom</t>
+          <t>Nở Hoa Tacetite</t>
         </is>
       </c>
       <c r="N414" t="inlineStr">
@@ -29484,7 +29484,7 @@
       </c>
       <c r="M415" t="inlineStr">
         <is>
-          <t>Destroyer's Promise</t>
+          <t>Lời Hứa Của Kẻ Hủy Diệt</t>
         </is>
       </c>
       <c r="N415" t="inlineStr">
@@ -29554,7 +29554,7 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>Relief Spring</t>
+          <t>Suối Giải Cảm</t>
         </is>
       </c>
       <c r="N416" t="inlineStr">
@@ -29624,7 +29624,7 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>Vibrant Lightning</t>
+          <t>Tia Chớp Sôi Động</t>
         </is>
       </c>
       <c r="N417" t="inlineStr">
@@ -29694,7 +29694,7 @@
       </c>
       <c r="M418" t="inlineStr">
         <is>
-          <t>Trái Tim Lôi</t>
+          <t>Trái Tim Điện</t>
         </is>
       </c>
       <c r="N418" t="inlineStr">
@@ -29764,7 +29764,7 @@
       </c>
       <c r="M419" t="inlineStr">
         <is>
-          <t>Patterned Nut</t>
+          <t>Hạt Dinh Dưỡng Mẫu</t>
         </is>
       </c>
       <c r="N419" t="inlineStr">
@@ -29834,7 +29834,7 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>Spring</t>
+          <t>Mùa Xuân</t>
         </is>
       </c>
       <c r="N420" t="inlineStr">
@@ -29904,7 +29904,7 @@
       </c>
       <c r="M421" t="inlineStr">
         <is>
-          <t>Irregular Aromatherapy</t>
+          <t>Liệu Pháp Mùi Hương Bất Thường</t>
         </is>
       </c>
       <c r="N421" t="inlineStr">
@@ -29974,7 +29974,7 @@
       </c>
       <c r="M422" t="inlineStr">
         <is>
-          <t>Thermal-Conduction Parts</t>
+          <t>Linh Kiện Dẫn Nhiệt</t>
         </is>
       </c>
       <c r="N422" t="inlineStr">
@@ -30044,7 +30044,7 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>Unlabeled Sample</t>
+          <t>Mẫu Không Nhãn</t>
         </is>
       </c>
       <c r="N423" t="inlineStr">
@@ -30114,7 +30114,7 @@
       </c>
       <c r="M424" t="inlineStr">
         <is>
-          <t>Iron Conch</t>
+          <t>Ốc Sắt</t>
         </is>
       </c>
       <c r="N424" t="inlineStr">
@@ -30184,7 +30184,7 @@
       </c>
       <c r="M425" t="inlineStr">
         <is>
-          <t>Compound Spring</t>
+          <t>Lò Xo Ghép</t>
         </is>
       </c>
       <c r="N425" t="inlineStr">
@@ -30254,7 +30254,7 @@
       </c>
       <c r="M426" t="inlineStr">
         <is>
-          <t>Soldier's Dog Tag</t>
+          <t>Thẻ bài của người lính</t>
         </is>
       </c>
       <c r="N426" t="inlineStr">
@@ -30324,7 +30324,7 @@
       </c>
       <c r="M427" t="inlineStr">
         <is>
-          <t>Torridity Rescuer</t>
+          <t>Vị cứu tinh nhiệt huyết</t>
         </is>
       </c>
       <c r="N427" t="inlineStr">
@@ -30394,7 +30394,7 @@
       </c>
       <c r="M428" t="inlineStr">
         <is>
-          <t>Inferior Spring</t>
+          <t>Mùa Xuân Thấp Kém</t>
         </is>
       </c>
       <c r="N428" t="inlineStr">
@@ -30464,7 +30464,7 @@
       </c>
       <c r="M429" t="inlineStr">
         <is>
-          <t>Exquisite Tacetite Bloom</t>
+          <t>Đóa Tacetite Tuyệt Mỹ</t>
         </is>
       </c>
       <c r="N429" t="inlineStr">
@@ -30604,7 +30604,7 @@
       </c>
       <c r="M431" t="inlineStr">
         <is>
-          <t>Emerald</t>
+          <t>Ngọc Lục Bảo</t>
         </is>
       </c>
       <c r="N431" t="inlineStr">
@@ -30674,7 +30674,7 @@
       </c>
       <c r="M432" t="inlineStr">
         <is>
-          <t>Concentrated Tonic</t>
+          <t>Thuốc Bổ Cô Đặc</t>
         </is>
       </c>
       <c r="N432" t="inlineStr">
@@ -30744,7 +30744,7 @@
       </c>
       <c r="M433" t="inlineStr">
         <is>
-          <t>Old Revolver</t>
+          <t>Khẩu Súng Lục Cũ</t>
         </is>
       </c>
       <c r="N433" t="inlineStr">
@@ -30814,7 +30814,7 @@
       </c>
       <c r="M434" t="inlineStr">
         <is>
-          <t>Stormcloud Canvas</t>
+          <t>Bức Tranh Mây Bão</t>
         </is>
       </c>
       <c r="N434" t="inlineStr">
@@ -30884,7 +30884,7 @@
       </c>
       <c r="M435" t="inlineStr">
         <is>
-          <t>Công Thức của Giấc Mơ</t>
+          <t>Công Thức Mộng Ảo</t>
         </is>
       </c>
       <c r="N435" t="inlineStr">
@@ -30954,7 +30954,7 @@
       </c>
       <c r="M436" t="inlineStr">
         <is>
-          <t>Dũng Khí của Feilian</t>
+          <t>Dũng khí của Phi Liên</t>
         </is>
       </c>
       <c r="N436" t="inlineStr">
@@ -31024,7 +31024,7 @@
       </c>
       <c r="M437" t="inlineStr">
         <is>
-          <t>Super Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Cấp Siêu</t>
         </is>
       </c>
       <c r="N437" t="inlineStr">
@@ -31164,7 +31164,7 @@
       </c>
       <c r="M439" t="inlineStr">
         <is>
-          <t>Comb</t>
+          <t>Lược</t>
         </is>
       </c>
       <c r="N439" t="inlineStr">
@@ -31234,7 +31234,7 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>Mildly Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Nhẹ</t>
         </is>
       </c>
       <c r="N440" t="inlineStr">
@@ -31304,7 +31304,7 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>Spirited Palettes</t>
+          <t>Bảng Màu Tinh Anh</t>
         </is>
       </c>
       <c r="N441" t="inlineStr">
@@ -31444,7 +31444,7 @@
       </c>
       <c r="M443" t="inlineStr">
         <is>
-          <t>Gust Canvas</t>
+          <t>Bức Tranh Gió</t>
         </is>
       </c>
       <c r="N443" t="inlineStr">
@@ -31514,7 +31514,7 @@
       </c>
       <c r="M444" t="inlineStr">
         <is>
-          <t>Phổ Biến Dạng</t>
+          <t>Phổ Bóp Méo</t>
         </is>
       </c>
       <c r="N444" t="inlineStr">
@@ -31584,7 +31584,7 @@
       </c>
       <c r="M445" t="inlineStr">
         <is>
-          <t>Improved Terminal</t>
+          <t>Thiết Bị Đầu Cuối Cải Tiến</t>
         </is>
       </c>
       <c r="N445" t="inlineStr">
@@ -31654,7 +31654,7 @@
       </c>
       <c r="M446" t="inlineStr">
         <is>
-          <t>Wind Seeker</t>
+          <t>Kẻ Tìm Gió</t>
         </is>
       </c>
       <c r="N446" t="inlineStr">
@@ -31724,7 +31724,7 @@
       </c>
       <c r="M447" t="inlineStr">
         <is>
-          <t>Severely Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Nặng</t>
         </is>
       </c>
       <c r="N447" t="inlineStr">
@@ -31794,7 +31794,7 @@
       </c>
       <c r="M448" t="inlineStr">
         <is>
-          <t>Modernized Device</t>
+          <t>Thiết Bị Hiện Đại Hóa</t>
         </is>
       </c>
       <c r="N448" t="inlineStr">
@@ -31864,7 +31864,7 @@
       </c>
       <c r="M449" t="inlineStr">
         <is>
-          <t>Moderately Mutated Structure</t>
+          <t>Cấu Trúc Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N449" t="inlineStr">
@@ -31934,7 +31934,7 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>Phổ Cực Hạn</t>
+          <t>Phổ Cực Đoan</t>
         </is>
       </c>
       <c r="N450" t="inlineStr">
@@ -32004,7 +32004,7 @@
       </c>
       <c r="M451" t="inlineStr">
         <is>
-          <t>Calculation Goggles</t>
+          <t>Kính Tính Toán</t>
         </is>
       </c>
       <c r="N451" t="inlineStr">
@@ -32074,7 +32074,7 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>"Tất cả-Seeing Eye"</t>
+          <t>"Con Mắt Toàn Tri"</t>
         </is>
       </c>
       <c r="N452" t="inlineStr">
@@ -32144,7 +32144,7 @@
       </c>
       <c r="M453" t="inlineStr">
         <is>
-          <t>Sweet Lotus Seed</t>
+          <t>Hạt Sen Ngọt</t>
         </is>
       </c>
       <c r="N453" t="inlineStr">
@@ -32214,7 +32214,7 @@
       </c>
       <c r="M454" t="inlineStr">
         <is>
-          <t>Trái Tim Cơ Khí</t>
+          <t>Trái Tim Bánh Răng</t>
         </is>
       </c>
       <c r="N454" t="inlineStr">
@@ -32284,7 +32284,7 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>Guardian's Proof</t>
+          <t>Chứng Cứ Người Bảo Vệ</t>
         </is>
       </c>
       <c r="N455" t="inlineStr">
@@ -32424,7 +32424,7 @@
       </c>
       <c r="M457" t="inlineStr">
         <is>
-          <t>Gearworks</t>
+          <t>Xưởng Cơ Khí</t>
         </is>
       </c>
       <c r="N457" t="inlineStr">
@@ -32494,7 +32494,7 @@
       </c>
       <c r="M458" t="inlineStr">
         <is>
-          <t>Cơ Khí của Điều Không Tưởng</t>
+          <t>Xưởng Cơ Khí Vô Tưởng</t>
         </is>
       </c>
       <c r="N458" t="inlineStr">
@@ -32564,7 +32564,7 @@
       </c>
       <c r="M459" t="inlineStr">
         <is>
-          <t>Giấc Mơ Cao Nguyên</t>
+          <t>Giấc Mộng Cao Nguyên</t>
         </is>
       </c>
       <c r="N459" t="inlineStr">
@@ -32634,7 +32634,7 @@
       </c>
       <c r="M460" t="inlineStr">
         <is>
-          <t>Heart Chainwheel</t>
+          <t>Bánh Xe Trái Tim</t>
         </is>
       </c>
       <c r="N460" t="inlineStr">
@@ -32704,7 +32704,7 @@
       </c>
       <c r="M461" t="inlineStr">
         <is>
-          <t>Chaos Mark</t>
+          <t>Dấu Hiệu Hỗn Loạn</t>
         </is>
       </c>
       <c r="N461" t="inlineStr">
@@ -32774,7 +32774,7 @@
       </c>
       <c r="M462" t="inlineStr">
         <is>
-          <t>Chaos Black Tea</t>
+          <t>Trà Hỗn Loạn</t>
         </is>
       </c>
       <c r="N462" t="inlineStr">
@@ -32844,7 +32844,7 @@
       </c>
       <c r="M463" t="inlineStr">
         <is>
-          <t>Destroyer's Codex</t>
+          <t>Bộ Quy Tắc Của Kẻ Hủy Diệt</t>
         </is>
       </c>
       <c r="N463" t="inlineStr">
@@ -33054,7 +33054,7 @@
       </c>
       <c r="M466" t="inlineStr">
         <is>
-          <t>Timeworn Comb</t>
+          <t>Lược Cũ Mòn</t>
         </is>
       </c>
       <c r="N466" t="inlineStr">
@@ -33124,7 +33124,7 @@
       </c>
       <c r="M467" t="inlineStr">
         <is>
-          <t>Severely Mutated Sample</t>
+          <t>Mẫu Vật Chất Đột Biến Nặng</t>
         </is>
       </c>
       <c r="N467" t="inlineStr">
@@ -33194,7 +33194,7 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>Old Device II</t>
+          <t>Thiết Bị Cũ II</t>
         </is>
       </c>
       <c r="N468" t="inlineStr">
@@ -33264,7 +33264,7 @@
       </c>
       <c r="M469" t="inlineStr">
         <is>
-          <t>Mystic Canvas</t>
+          <t>Bức Tranh Huyền Bí</t>
         </is>
       </c>
       <c r="N469" t="inlineStr">
@@ -33334,7 +33334,7 @@
       </c>
       <c r="M470" t="inlineStr">
         <is>
-          <t>Repair Kit</t>
+          <t>Bộ Dụng Cụ Sửa Chữa</t>
         </is>
       </c>
       <c r="N470" t="inlineStr">
@@ -33404,7 +33404,7 @@
       </c>
       <c r="M471" t="inlineStr">
         <is>
-          <t>Red Needle</t>
+          <t>Kim Đỏ</t>
         </is>
       </c>
       <c r="N471" t="inlineStr">
@@ -33474,7 +33474,7 @@
       </c>
       <c r="M472" t="inlineStr">
         <is>
-          <t>Nhánh Cây Dưới Đáy Biển</t>
+          <t>Nhánh Dưới Đáy Biển</t>
         </is>
       </c>
       <c r="N472" t="inlineStr">
@@ -33544,7 +33544,7 @@
       </c>
       <c r="M473" t="inlineStr">
         <is>
-          <t>Prisoner Unchained</t>
+          <t>Tù Nhân Được Giải Xiềng</t>
         </is>
       </c>
       <c r="N473" t="inlineStr">
@@ -33614,7 +33614,7 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>Moderately Mutated Sample</t>
+          <t>Mẫu Đột Biến Mức Trung Bình</t>
         </is>
       </c>
       <c r="N474" t="inlineStr">
@@ -33684,7 +33684,7 @@
       </c>
       <c r="M475" t="inlineStr">
         <is>
-          <t>Chaos Marshmallow</t>
+          <t>Kẹo Dẻo Hỗn Loạn</t>
         </is>
       </c>
       <c r="N475" t="inlineStr">
@@ -33754,7 +33754,7 @@
       </c>
       <c r="M476" t="inlineStr">
         <is>
-          <t>Alloy Relief Spring</t>
+          <t>Lò Xo Giảm Chấn Hợp Kim</t>
         </is>
       </c>
       <c r="N476" t="inlineStr">
@@ -33824,7 +33824,7 @@
       </c>
       <c r="M477" t="inlineStr">
         <is>
-          <t>Dangerous Data</t>
+          <t>Dữ liệu nguy hiểm</t>
         </is>
       </c>
       <c r="N477" t="inlineStr">
@@ -33894,7 +33894,7 @@
       </c>
       <c r="M478" t="inlineStr">
         <is>
-          <t>Compound Gear</t>
+          <t>Bánh Răng Ghép</t>
         </is>
       </c>
       <c r="N478" t="inlineStr">
@@ -33964,7 +33964,7 @@
       </c>
       <c r="M479" t="inlineStr">
         <is>
-          <t>Hidden Blade</t>
+          <t>Lưỡi Kiếm Ẩn</t>
         </is>
       </c>
       <c r="N479" t="inlineStr">
@@ -34034,7 +34034,7 @@
       </c>
       <c r="M480" t="inlineStr">
         <is>
-          <t>Compound Nut</t>
+          <t>Đai Ốc Ghép</t>
         </is>
       </c>
       <c r="N480" t="inlineStr">
@@ -34174,7 +34174,7 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>Chìa Khóa Hỗn Độn</t>
+          <t>Chìa Khóa Hỗn Loạn</t>
         </is>
       </c>
       <c r="N482" t="inlineStr">
@@ -34244,7 +34244,7 @@
       </c>
       <c r="M483" t="inlineStr">
         <is>
-          <t>Insulation Parts</t>
+          <t>Linh kiện cách nhiệt</t>
         </is>
       </c>
       <c r="N483" t="inlineStr">
@@ -34384,7 +34384,7 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>Watcher's Codex</t>
+          <t>Bộ Luật Giám Thị</t>
         </is>
       </c>
       <c r="N485" t="inlineStr">
@@ -34524,7 +34524,7 @@
       </c>
       <c r="M487" t="inlineStr">
         <is>
-          <t>Power Hammer</t>
+          <t>Búa Năng Lượng</t>
         </is>
       </c>
       <c r="N487" t="inlineStr">
@@ -34594,7 +34594,7 @@
       </c>
       <c r="M488" t="inlineStr">
         <is>
-          <t>Bạc Của Người Quan Sát</t>
+          <t>Bạc của Người Quan Sát</t>
         </is>
       </c>
       <c r="N488" t="inlineStr">
@@ -34664,7 +34664,7 @@
       </c>
       <c r="M489" t="inlineStr">
         <is>
-          <t>Trái Tim Quang Phổ</t>
+          <t>Trái Tim Spectro</t>
         </is>
       </c>
       <c r="N489" t="inlineStr">
@@ -34734,7 +34734,7 @@
       </c>
       <c r="M490" t="inlineStr">
         <is>
-          <t>Blue Night Waltz</t>
+          <t>Điệu Van-xơ Đêm Xanh</t>
         </is>
       </c>
       <c r="N490" t="inlineStr">
@@ -34804,7 +34804,7 @@
       </c>
       <c r="M491" t="inlineStr">
         <is>
-          <t>Mechanical Wing</t>
+          <t>Cánh Cơ Khí</t>
         </is>
       </c>
       <c r="N491" t="inlineStr">
@@ -34874,7 +34874,7 @@
       </c>
       <c r="M492" t="inlineStr">
         <is>
-          <t>Tracking Goggles</t>
+          <t>Kính Theo Dõi</t>
         </is>
       </c>
       <c r="N492" t="inlineStr">
@@ -34944,7 +34944,7 @@
       </c>
       <c r="M493" t="inlineStr">
         <is>
-          <t>Wonderland Phantasm</t>
+          <t>Ảo Ảnh Kỳ Diệu</t>
         </is>
       </c>
       <c r="N493" t="inlineStr">
@@ -35014,7 +35014,7 @@
       </c>
       <c r="M494" t="inlineStr">
         <is>
-          <t>Golden Compass</t>
+          <t>La bàn Vàng</t>
         </is>
       </c>
       <c r="N494" t="inlineStr">
@@ -35084,7 +35084,7 @@
       </c>
       <c r="M495" t="inlineStr">
         <is>
-          <t>Captain's Dog Tag</t>
+          <t>Thẻ bài của Đại úy</t>
         </is>
       </c>
       <c r="N495" t="inlineStr">
@@ -35154,7 +35154,7 @@
       </c>
       <c r="M496" t="inlineStr">
         <is>
-          <t>Attack Whistle</t>
+          <t>Tấn Công Theo Hiệu Lệnh</t>
         </is>
       </c>
       <c r="N496" t="inlineStr">
@@ -35224,7 +35224,7 @@
       </c>
       <c r="M497" t="inlineStr">
         <is>
-          <t>Blue Crystal</t>
+          <t>Pha Lê Xanh</t>
         </is>
       </c>
       <c r="N497" t="inlineStr">
@@ -35364,7 +35364,7 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>Compass</t>
+          <t>La bàn</t>
         </is>
       </c>
       <c r="N499" t="inlineStr">
@@ -35434,7 +35434,7 @@
       </c>
       <c r="M500" t="inlineStr">
         <is>
-          <t>Medic Kit</t>
+          <t>Bộ Dụng Cụ Y Tế</t>
         </is>
       </c>
       <c r="N500" t="inlineStr">
